--- a/research/traditional_assets/database/data/switzerland/switzerland_software_entertainment.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_software_entertainment.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.104434679691828</v>
+        <v>0.1043206350594779</v>
       </c>
       <c r="C2">
-        <v>25.06543593464282</v>
+        <v>24.84524383570512</v>
       </c>
       <c r="D2">
-        <v>22.87543593464282</v>
+        <v>22.90917580451627</v>
       </c>
       <c r="E2">
-        <v>-3.893196881115593</v>
+        <v>-3.639264912304437</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.2539319688111559</v>
       </c>
       <c r="G2">
         <v>2.19</v>
@@ -1439,28 +1439,28 @@
         <v>1.772</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01277277803120114</v>
       </c>
       <c r="N2">
-        <v>1.772</v>
+        <v>1.759227221968798</v>
       </c>
       <c r="O2">
-        <v>0.2587119999999999</v>
+        <v>0.2568471744074445</v>
       </c>
       <c r="P2">
-        <v>1.513288</v>
+        <v>1.502380047561354</v>
       </c>
       <c r="Q2">
-        <v>2.156288</v>
+        <v>2.145380047561354</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.104434679691828</v>
+        <v>0.1049404778378565</v>
       </c>
       <c r="T2">
-        <v>1.354149646462541</v>
+        <v>1.365830896948187</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>138.7325447660161</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1043206350594779</v>
+        <v>0.1042065904271279</v>
       </c>
       <c r="C3">
-        <v>24.84524383570512</v>
+        <v>24.6251514122745</v>
       </c>
       <c r="D3">
-        <v>22.90917580451627</v>
+        <v>22.94301534989681</v>
       </c>
       <c r="E3">
-        <v>-3.639264912304437</v>
+        <v>-3.385332943493281</v>
       </c>
       <c r="F3">
-        <v>0.2539319688111559</v>
+        <v>0.5078639376223119</v>
       </c>
       <c r="G3">
         <v>2.19</v>
@@ -1521,28 +1521,28 @@
         <v>1.772</v>
       </c>
       <c r="M3">
-        <v>0.01277277803120114</v>
+        <v>0.02554555606240229</v>
       </c>
       <c r="N3">
-        <v>1.759227221968798</v>
+        <v>1.746454443937597</v>
       </c>
       <c r="O3">
-        <v>0.2568471744074445</v>
+        <v>0.2549823488148892</v>
       </c>
       <c r="P3">
-        <v>1.502380047561354</v>
+        <v>1.491472095122708</v>
       </c>
       <c r="Q3">
-        <v>2.145380047561354</v>
+        <v>2.134472095122708</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1049404778378565</v>
+        <v>0.1054565983950284</v>
       </c>
       <c r="T3">
-        <v>1.365830896948187</v>
+        <v>1.377750540300888</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>138.7325447660161</v>
+        <v>69.36627238300805</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1042065904271279</v>
+        <v>0.1040925457947778</v>
       </c>
       <c r="C4">
-        <v>24.6251514122745</v>
+        <v>24.40515910670171</v>
       </c>
       <c r="D4">
-        <v>22.94301534989681</v>
+        <v>22.97695501313517</v>
       </c>
       <c r="E4">
-        <v>-3.385332943493281</v>
+        <v>-3.131400974682125</v>
       </c>
       <c r="F4">
-        <v>0.5078639376223119</v>
+        <v>0.7617959064334677</v>
       </c>
       <c r="G4">
         <v>2.19</v>
@@ -1603,28 +1603,28 @@
         <v>1.772</v>
       </c>
       <c r="M4">
-        <v>0.02554555606240229</v>
+        <v>0.03831833409360343</v>
       </c>
       <c r="N4">
-        <v>1.746454443937597</v>
+        <v>1.733681665906396</v>
       </c>
       <c r="O4">
-        <v>0.2549823488148892</v>
+        <v>0.2531175232223338</v>
       </c>
       <c r="P4">
-        <v>1.491472095122708</v>
+        <v>1.480564142684062</v>
       </c>
       <c r="Q4">
-        <v>2.134472095122708</v>
+        <v>2.123564142684062</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1054565983950284</v>
+        <v>0.105983360613173</v>
       </c>
       <c r="T4">
-        <v>1.377750540300888</v>
+        <v>1.389915949495912</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>69.36627238300805</v>
+        <v>46.24418158867203</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1040925457947778</v>
+        <v>0.1039785011624277</v>
       </c>
       <c r="C5">
-        <v>24.40515910670171</v>
+        <v>24.18526736395881</v>
       </c>
       <c r="D5">
-        <v>22.97695501313517</v>
+        <v>23.01099523920344</v>
       </c>
       <c r="E5">
-        <v>-3.131400974682125</v>
+        <v>-2.877469005870969</v>
       </c>
       <c r="F5">
-        <v>0.7617959064334677</v>
+        <v>1.015727875244624</v>
       </c>
       <c r="G5">
         <v>2.19</v>
@@ -1685,28 +1685,28 @@
         <v>1.772</v>
       </c>
       <c r="M5">
-        <v>0.03831833409360343</v>
+        <v>0.05109111212480457</v>
       </c>
       <c r="N5">
-        <v>1.733681665906396</v>
+        <v>1.720908887875195</v>
       </c>
       <c r="O5">
-        <v>0.2531175232223338</v>
+        <v>0.2512526976297785</v>
       </c>
       <c r="P5">
-        <v>1.480564142684062</v>
+        <v>1.469656190245417</v>
       </c>
       <c r="Q5">
-        <v>2.123564142684062</v>
+        <v>2.112656190245417</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.105983360613173</v>
+        <v>0.1065210970441955</v>
       </c>
       <c r="T5">
-        <v>1.389915949495912</v>
+        <v>1.402334804715833</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>46.24418158867203</v>
+        <v>34.68313619150403</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1039785011624277</v>
+        <v>0.1038644565300777</v>
       </c>
       <c r="C6">
-        <v>24.18526736395881</v>
+        <v>23.96547663165871</v>
       </c>
       <c r="D6">
-        <v>23.01099523920344</v>
+        <v>23.04513647571449</v>
       </c>
       <c r="E6">
-        <v>-2.877469005870969</v>
+        <v>-2.623537037059813</v>
       </c>
       <c r="F6">
-        <v>1.015727875244624</v>
+        <v>1.26965984405578</v>
       </c>
       <c r="G6">
         <v>2.19</v>
@@ -1767,28 +1767,28 @@
         <v>1.772</v>
       </c>
       <c r="M6">
-        <v>0.05109111212480457</v>
+        <v>0.06386389015600571</v>
       </c>
       <c r="N6">
-        <v>1.720908887875195</v>
+        <v>1.708136109843994</v>
       </c>
       <c r="O6">
-        <v>0.2512526976297785</v>
+        <v>0.2493878720372231</v>
       </c>
       <c r="P6">
-        <v>1.469656190245417</v>
+        <v>1.458748237806771</v>
       </c>
       <c r="Q6">
-        <v>2.112656190245417</v>
+        <v>2.10174823780677</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1065210970441955</v>
+        <v>0.107070154242187</v>
       </c>
       <c r="T6">
-        <v>1.402334804715833</v>
+        <v>1.415015109519331</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>34.68313619150403</v>
+        <v>27.74650895320322</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1038644565300777</v>
+        <v>0.1037504118977276</v>
       </c>
       <c r="C7">
-        <v>23.96547663165871</v>
+        <v>23.74578736007472</v>
       </c>
       <c r="D7">
-        <v>23.04513647571449</v>
+        <v>23.07937917294165</v>
       </c>
       <c r="E7">
-        <v>-2.623537037059813</v>
+        <v>-2.369605068248657</v>
       </c>
       <c r="F7">
-        <v>1.26965984405578</v>
+        <v>1.523591812866936</v>
       </c>
       <c r="G7">
         <v>2.19</v>
@@ -1849,28 +1849,28 @@
         <v>1.772</v>
       </c>
       <c r="M7">
-        <v>0.06386389015600571</v>
+        <v>0.07663666818720687</v>
       </c>
       <c r="N7">
-        <v>1.708136109843994</v>
+        <v>1.695363331812793</v>
       </c>
       <c r="O7">
-        <v>0.2493878720372231</v>
+        <v>0.2475230464446677</v>
       </c>
       <c r="P7">
-        <v>1.458748237806771</v>
+        <v>1.447840285368125</v>
       </c>
       <c r="Q7">
-        <v>2.10174823780677</v>
+        <v>2.090840285368125</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.107070154242187</v>
+        <v>0.1076308935082208</v>
       </c>
       <c r="T7">
-        <v>1.415015109519331</v>
+        <v>1.427965208042052</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>27.74650895320322</v>
+        <v>23.12209079433601</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1037504118977276</v>
+        <v>0.1036363672653775</v>
       </c>
       <c r="C8">
-        <v>23.74578736007472</v>
+        <v>23.52620000216037</v>
       </c>
       <c r="D8">
-        <v>23.07937917294165</v>
+        <v>23.11372378383846</v>
       </c>
       <c r="E8">
-        <v>-2.369605068248657</v>
+        <v>-2.115673099437501</v>
       </c>
       <c r="F8">
-        <v>1.523591812866935</v>
+        <v>1.777523781678091</v>
       </c>
       <c r="G8">
         <v>2.19</v>
@@ -1931,28 +1931,28 @@
         <v>1.772</v>
       </c>
       <c r="M8">
-        <v>0.07663666818720685</v>
+        <v>0.08940944621840799</v>
       </c>
       <c r="N8">
-        <v>1.695363331812793</v>
+        <v>1.682590553781592</v>
       </c>
       <c r="O8">
-        <v>0.2475230464446677</v>
+        <v>0.2456582208521123</v>
       </c>
       <c r="P8">
-        <v>1.447840285368125</v>
+        <v>1.436932332929479</v>
       </c>
       <c r="Q8">
-        <v>2.090840285368125</v>
+        <v>2.079932332929479</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1076308935082208</v>
+        <v>0.1082036916832016</v>
       </c>
       <c r="T8">
-        <v>1.427965208042052</v>
+        <v>1.441193803307198</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.12209079433602</v>
+        <v>19.81893496657373</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1036363672653775</v>
+        <v>0.1035223226330274</v>
       </c>
       <c r="C9">
-        <v>23.52620000216037</v>
+        <v>23.3067150135694</v>
       </c>
       <c r="D9">
-        <v>23.11372378383846</v>
+        <v>23.14817076405864</v>
       </c>
       <c r="E9">
-        <v>-2.115673099437501</v>
+        <v>-1.861741130626345</v>
       </c>
       <c r="F9">
-        <v>1.777523781678092</v>
+        <v>2.031455750489247</v>
       </c>
       <c r="G9">
         <v>2.19</v>
@@ -2013,28 +2013,28 @@
         <v>1.772</v>
       </c>
       <c r="M9">
-        <v>0.089409446218408</v>
+        <v>0.1021822242496091</v>
       </c>
       <c r="N9">
-        <v>1.682590553781592</v>
+        <v>1.66981777575039</v>
       </c>
       <c r="O9">
-        <v>0.2456582208521123</v>
+        <v>0.243793395259557</v>
       </c>
       <c r="P9">
-        <v>1.436932332929479</v>
+        <v>1.426024380490833</v>
       </c>
       <c r="Q9">
-        <v>2.079932332929479</v>
+        <v>2.069024380490833</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1082036916832016</v>
+        <v>0.1087889419924211</v>
       </c>
       <c r="T9">
-        <v>1.441193803307198</v>
+        <v>1.454709976730281</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.81893496657373</v>
+        <v>17.34156809575201</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1035223226330274</v>
+        <v>0.1034082780006774</v>
       </c>
       <c r="C10">
-        <v>23.3067150135694</v>
+        <v>23.08733285267587</v>
       </c>
       <c r="D10">
-        <v>23.14817076405864</v>
+        <v>23.18272057197628</v>
       </c>
       <c r="E10">
-        <v>-1.861741130626345</v>
+        <v>-1.607809161815189</v>
       </c>
       <c r="F10">
-        <v>2.031455750489247</v>
+        <v>2.285387719300403</v>
       </c>
       <c r="G10">
         <v>2.19</v>
@@ -2095,28 +2095,28 @@
         <v>1.772</v>
       </c>
       <c r="M10">
-        <v>0.1021822242496091</v>
+        <v>0.1149550022808103</v>
       </c>
       <c r="N10">
-        <v>1.66981777575039</v>
+        <v>1.657044997719189</v>
       </c>
       <c r="O10">
-        <v>0.243793395259557</v>
+        <v>0.2419285696670016</v>
       </c>
       <c r="P10">
-        <v>1.426024380490833</v>
+        <v>1.415116428052188</v>
       </c>
       <c r="Q10">
-        <v>2.069024380490833</v>
+        <v>2.058116428052188</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1087889419924211</v>
+        <v>0.1093870549457993</v>
       </c>
       <c r="T10">
-        <v>1.454709976730281</v>
+        <v>1.468523208909915</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.34156809575201</v>
+        <v>15.41472719622401</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1034082780006774</v>
+        <v>0.1032942333683273</v>
       </c>
       <c r="C11">
-        <v>23.08733285267587</v>
+        <v>22.86805398059456</v>
       </c>
       <c r="D11">
-        <v>23.18272057197628</v>
+        <v>23.21737366870612</v>
       </c>
       <c r="E11">
-        <v>-1.607809161815189</v>
+        <v>-1.353877193004033</v>
       </c>
       <c r="F11">
-        <v>2.285387719300403</v>
+        <v>2.539319688111559</v>
       </c>
       <c r="G11">
         <v>2.19</v>
@@ -2177,28 +2177,28 @@
         <v>1.772</v>
       </c>
       <c r="M11">
-        <v>0.1149550022808103</v>
+        <v>0.1277277803120114</v>
       </c>
       <c r="N11">
-        <v>1.657044997719189</v>
+        <v>1.644272219687988</v>
       </c>
       <c r="O11">
-        <v>0.2419285696670016</v>
+        <v>0.2400637440744463</v>
       </c>
       <c r="P11">
-        <v>1.415116428052188</v>
+        <v>1.404208475613542</v>
       </c>
       <c r="Q11">
-        <v>2.058116428052188</v>
+        <v>2.047208475613542</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1093870549457993</v>
+        <v>0.1099984592981414</v>
       </c>
       <c r="T11">
-        <v>1.468523208909915</v>
+        <v>1.482643401804653</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.41472719622401</v>
+        <v>13.87325447660161</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1032942333683273</v>
+        <v>0.1033210987359772</v>
       </c>
       <c r="C12">
-        <v>22.86805398059456</v>
+        <v>22.60594949574472</v>
       </c>
       <c r="D12">
-        <v>23.21737366870612</v>
+        <v>23.20920115266743</v>
       </c>
       <c r="E12">
-        <v>-1.353877193004033</v>
+        <v>-1.099945224192878</v>
       </c>
       <c r="F12">
-        <v>2.53931968811156</v>
+        <v>2.793251656922715</v>
       </c>
       <c r="G12">
         <v>2.19</v>
@@ -2259,45 +2259,45 @@
         <v>1.772</v>
       </c>
       <c r="M12">
-        <v>0.1277277803120114</v>
+        <v>0.1446904358285966</v>
       </c>
       <c r="N12">
-        <v>1.644272219687988</v>
+        <v>1.627309564171403</v>
       </c>
       <c r="O12">
-        <v>0.2400637440744463</v>
+        <v>0.2375871963690248</v>
       </c>
       <c r="P12">
-        <v>1.404208475613542</v>
+        <v>1.389722367802378</v>
       </c>
       <c r="Q12">
-        <v>2.047208475613542</v>
+        <v>2.032722367802378</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1099984592981414</v>
+        <v>0.1106236030741317</v>
       </c>
       <c r="T12">
-        <v>1.482643401804653</v>
+        <v>1.49708090240489</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.146</v>
       </c>
       <c r="W12">
-        <v>0.0429562</v>
+        <v>0.0442372</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.87325447660161</v>
+        <v>12.24683573487295</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1033210987359772</v>
+        <v>0.1032198641036272</v>
       </c>
       <c r="C13">
-        <v>22.60594949574472</v>
+        <v>22.38284341813826</v>
       </c>
       <c r="D13">
-        <v>23.20920115266743</v>
+        <v>23.24002704387213</v>
       </c>
       <c r="E13">
-        <v>-1.099945224192878</v>
+        <v>-0.8460132553817217</v>
       </c>
       <c r="F13">
-        <v>2.793251656922715</v>
+        <v>3.047183625733871</v>
       </c>
       <c r="G13">
         <v>2.19</v>
@@ -2341,28 +2341,28 @@
         <v>1.772</v>
       </c>
       <c r="M13">
-        <v>0.1446904358285966</v>
+        <v>0.1578441118130145</v>
       </c>
       <c r="N13">
-        <v>1.627309564171403</v>
+        <v>1.614155888186985</v>
       </c>
       <c r="O13">
-        <v>0.2375871963690248</v>
+        <v>0.2356667596752998</v>
       </c>
       <c r="P13">
-        <v>1.389722367802378</v>
+        <v>1.378489128511685</v>
       </c>
       <c r="Q13">
-        <v>2.032722367802378</v>
+        <v>2.021489128511686</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1106236030741317</v>
+        <v>0.1112629546632127</v>
       </c>
       <c r="T13">
-        <v>1.49708090240489</v>
+        <v>1.511846528018769</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.24683573487295</v>
+        <v>11.22626609030021</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1032198641036272</v>
+        <v>0.1031186294712771</v>
       </c>
       <c r="C14">
-        <v>22.38284341813826</v>
+        <v>22.15981933381718</v>
       </c>
       <c r="D14">
-        <v>23.24002704387213</v>
+        <v>23.27093492836221</v>
       </c>
       <c r="E14">
-        <v>-0.8460132553817217</v>
+        <v>-0.5920812865705654</v>
       </c>
       <c r="F14">
-        <v>3.047183625733871</v>
+        <v>3.301115594545027</v>
       </c>
       <c r="G14">
         <v>2.19</v>
@@ -2423,28 +2423,28 @@
         <v>1.772</v>
       </c>
       <c r="M14">
-        <v>0.1578441118130145</v>
+        <v>0.1709977877974324</v>
       </c>
       <c r="N14">
-        <v>1.614155888186985</v>
+        <v>1.601002212202567</v>
       </c>
       <c r="O14">
-        <v>0.2356667596752998</v>
+        <v>0.2337463229815748</v>
       </c>
       <c r="P14">
-        <v>1.378489128511685</v>
+        <v>1.367255889220992</v>
       </c>
       <c r="Q14">
-        <v>2.021489128511686</v>
+        <v>2.010255889220992</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1112629546632127</v>
+        <v>0.1119170039899737</v>
       </c>
       <c r="T14">
-        <v>1.511846528018769</v>
+        <v>1.526951593301933</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.22626609030021</v>
+        <v>10.36270716027711</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1031186294712771</v>
+        <v>0.1032206468389271</v>
       </c>
       <c r="C15">
-        <v>22.15981933381718</v>
+        <v>21.87474082392754</v>
       </c>
       <c r="D15">
-        <v>23.27093492836221</v>
+        <v>23.23978838728372</v>
       </c>
       <c r="E15">
-        <v>-0.5920812865705654</v>
+        <v>-0.3381493177594095</v>
       </c>
       <c r="F15">
-        <v>3.301115594545027</v>
+        <v>3.555047563356183</v>
       </c>
       <c r="G15">
         <v>2.19</v>
@@ -2505,45 +2505,45 @@
         <v>1.772</v>
       </c>
       <c r="M15">
-        <v>0.1709977877974324</v>
+        <v>0.1901950446395558</v>
       </c>
       <c r="N15">
-        <v>1.601002212202567</v>
+        <v>1.581804955360444</v>
       </c>
       <c r="O15">
-        <v>0.2337463229815748</v>
+        <v>0.2309435234826248</v>
       </c>
       <c r="P15">
-        <v>1.367255889220992</v>
+        <v>1.350861431877819</v>
       </c>
       <c r="Q15">
-        <v>2.010255889220992</v>
+        <v>1.993861431877819</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1119170039899737</v>
+        <v>0.1125862637661942</v>
       </c>
       <c r="T15">
-        <v>1.526951593301933</v>
+        <v>1.542407939173077</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.146</v>
       </c>
       <c r="W15">
-        <v>0.0442372</v>
+        <v>0.045689</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.36270716027711</v>
+        <v>9.316751671202416</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1032206468389271</v>
+        <v>0.103133930206577</v>
       </c>
       <c r="C16">
-        <v>21.87474082392754</v>
+        <v>21.64727866523504</v>
       </c>
       <c r="D16">
-        <v>23.23978838728372</v>
+        <v>23.26625819740238</v>
       </c>
       <c r="E16">
-        <v>-0.3381493177594095</v>
+        <v>-0.08421734894825317</v>
       </c>
       <c r="F16">
-        <v>3.555047563356183</v>
+        <v>3.808979532167339</v>
       </c>
       <c r="G16">
         <v>2.19</v>
@@ -2587,28 +2587,28 @@
         <v>1.772</v>
       </c>
       <c r="M16">
-        <v>0.1901950446395558</v>
+        <v>0.2037804049709526</v>
       </c>
       <c r="N16">
-        <v>1.581804955360444</v>
+        <v>1.568219595029047</v>
       </c>
       <c r="O16">
-        <v>0.2309435234826248</v>
+        <v>0.2289600608742408</v>
       </c>
       <c r="P16">
-        <v>1.350861431877819</v>
+        <v>1.339259534154806</v>
       </c>
       <c r="Q16">
-        <v>1.993861431877819</v>
+        <v>1.982259534154806</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1125862637661942</v>
+        <v>0.113271270831267</v>
       </c>
       <c r="T16">
-        <v>1.542407939173077</v>
+        <v>1.558227963770602</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.316751671202416</v>
+        <v>8.695634893122254</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.103133930206577</v>
+        <v>0.1030472135742269</v>
       </c>
       <c r="C17">
-        <v>21.64727866523505</v>
+        <v>21.41987687282283</v>
       </c>
       <c r="D17">
-        <v>23.26625819740238</v>
+        <v>23.29278837380132</v>
       </c>
       <c r="E17">
-        <v>-0.08421734894825406</v>
+        <v>0.1697146198629023</v>
       </c>
       <c r="F17">
-        <v>3.808979532167339</v>
+        <v>4.062911500978495</v>
       </c>
       <c r="G17">
         <v>2.19</v>
@@ -2669,28 +2669,28 @@
         <v>1.772</v>
       </c>
       <c r="M17">
-        <v>0.2037804049709526</v>
+        <v>0.2173657653023495</v>
       </c>
       <c r="N17">
-        <v>1.568219595029047</v>
+        <v>1.55463423469765</v>
       </c>
       <c r="O17">
-        <v>0.2289600608742408</v>
+        <v>0.2269765982658569</v>
       </c>
       <c r="P17">
-        <v>1.339259534154806</v>
+        <v>1.327657636431793</v>
       </c>
       <c r="Q17">
-        <v>1.982259534154806</v>
+        <v>1.970657636431793</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.113271270831267</v>
+        <v>0.1139725875883653</v>
       </c>
       <c r="T17">
-        <v>1.558227963770602</v>
+        <v>1.574424655620448</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.695634893122257</v>
+        <v>8.152157712302113</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1030472135742269</v>
+        <v>0.1029604969418768</v>
       </c>
       <c r="C18">
-        <v>21.41987687282283</v>
+        <v>21.19253565343101</v>
       </c>
       <c r="D18">
-        <v>23.29278837380132</v>
+        <v>23.31937912322066</v>
       </c>
       <c r="E18">
-        <v>0.1697146198629023</v>
+        <v>0.4236465886740586</v>
       </c>
       <c r="F18">
-        <v>4.062911500978495</v>
+        <v>4.316843469789651</v>
       </c>
       <c r="G18">
         <v>2.19</v>
@@ -2751,28 +2751,28 @@
         <v>1.772</v>
       </c>
       <c r="M18">
-        <v>0.2173657653023495</v>
+        <v>0.2309511256337463</v>
       </c>
       <c r="N18">
-        <v>1.55463423469765</v>
+        <v>1.541048874366253</v>
       </c>
       <c r="O18">
-        <v>0.2269765982658569</v>
+        <v>0.2249931356574729</v>
       </c>
       <c r="P18">
-        <v>1.327657636431793</v>
+        <v>1.31605573870878</v>
       </c>
       <c r="Q18">
-        <v>1.970657636431793</v>
+        <v>1.95905573870878</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1139725875883653</v>
+        <v>0.1146908035444299</v>
       </c>
       <c r="T18">
-        <v>1.574424655620448</v>
+        <v>1.591011629201615</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.152157712302113</v>
+        <v>7.672619023343165</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1029604969418768</v>
+        <v>0.1029967563095267</v>
       </c>
       <c r="C19">
-        <v>21.19253565343101</v>
+        <v>20.9274777463583</v>
       </c>
       <c r="D19">
-        <v>23.31937912322066</v>
+        <v>23.3082531849591</v>
       </c>
       <c r="E19">
-        <v>0.4236465886740586</v>
+        <v>0.6775785574852149</v>
       </c>
       <c r="F19">
-        <v>4.316843469789651</v>
+        <v>4.570775438600807</v>
       </c>
       <c r="G19">
         <v>2.19</v>
@@ -2833,45 +2833,45 @@
         <v>1.772</v>
       </c>
       <c r="M19">
-        <v>0.2309511256337463</v>
+        <v>0.2481931063160238</v>
       </c>
       <c r="N19">
-        <v>1.541048874366253</v>
+        <v>1.523806893683976</v>
       </c>
       <c r="O19">
-        <v>0.2249931356574729</v>
+        <v>0.2224758064778604</v>
       </c>
       <c r="P19">
-        <v>1.31605573870878</v>
+        <v>1.301331087206115</v>
       </c>
       <c r="Q19">
-        <v>1.95905573870878</v>
+        <v>1.944331087206115</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1146908035444299</v>
+        <v>0.1154265369628375</v>
       </c>
       <c r="T19">
-        <v>1.591011629201615</v>
+        <v>1.608003163114031</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.146</v>
       </c>
       <c r="W19">
-        <v>0.045689</v>
+        <v>0.0463722</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>7.672619023343165</v>
+        <v>7.139602007090862</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1029967563095267</v>
+        <v>0.1029168716771767</v>
       </c>
       <c r="C20">
-        <v>20.9274777463583</v>
+        <v>20.69807191461119</v>
       </c>
       <c r="D20">
-        <v>23.3082531849591</v>
+        <v>23.33277932202316</v>
       </c>
       <c r="E20">
-        <v>0.677578557485214</v>
+        <v>0.9315105262963703</v>
       </c>
       <c r="F20">
-        <v>4.570775438600807</v>
+        <v>4.824707407411963</v>
       </c>
       <c r="G20">
         <v>2.19</v>
@@ -2915,28 +2915,28 @@
         <v>1.772</v>
       </c>
       <c r="M20">
-        <v>0.2481931063160238</v>
+        <v>0.2619816122224696</v>
       </c>
       <c r="N20">
-        <v>1.523806893683976</v>
+        <v>1.51001838777753</v>
       </c>
       <c r="O20">
-        <v>0.2224758064778604</v>
+        <v>0.2204626846155193</v>
       </c>
       <c r="P20">
-        <v>1.301331087206115</v>
+        <v>1.289555703162011</v>
       </c>
       <c r="Q20">
-        <v>1.944331087206115</v>
+        <v>1.932555703162011</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1154265369628375</v>
+        <v>0.1161804366384897</v>
       </c>
       <c r="T20">
-        <v>1.608003163114031</v>
+        <v>1.625414241073667</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.139602007090863</v>
+        <v>6.76383348040187</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1029168716771767</v>
+        <v>0.1028369870448266</v>
       </c>
       <c r="C21">
-        <v>20.69807191461119</v>
+        <v>20.46871775254722</v>
       </c>
       <c r="D21">
-        <v>23.33277932202316</v>
+        <v>23.35735712877034</v>
       </c>
       <c r="E21">
-        <v>0.9315105262963703</v>
+        <v>1.185442495107527</v>
       </c>
       <c r="F21">
-        <v>4.824707407411963</v>
+        <v>5.078639376223119</v>
       </c>
       <c r="G21">
         <v>2.19</v>
@@ -2997,28 +2997,28 @@
         <v>1.772</v>
       </c>
       <c r="M21">
-        <v>0.2619816122224696</v>
+        <v>0.2757701181289154</v>
       </c>
       <c r="N21">
-        <v>1.51001838777753</v>
+        <v>1.496229881871084</v>
       </c>
       <c r="O21">
-        <v>0.2204626846155193</v>
+        <v>0.2184495627531783</v>
       </c>
       <c r="P21">
-        <v>1.289555703162011</v>
+        <v>1.277780319117906</v>
       </c>
       <c r="Q21">
-        <v>1.932555703162011</v>
+        <v>1.920780319117906</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1161804366384897</v>
+        <v>0.1169531838060333</v>
       </c>
       <c r="T21">
-        <v>1.625414241073667</v>
+        <v>1.643260595982293</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.76383348040187</v>
+        <v>6.425641806381776</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1028369870448266</v>
+        <v>0.1027571024124765</v>
       </c>
       <c r="C22">
-        <v>20.46871775254722</v>
+        <v>20.23941542361882</v>
       </c>
       <c r="D22">
-        <v>23.35735712877034</v>
+        <v>23.38198676865309</v>
       </c>
       <c r="E22">
-        <v>1.185442495107527</v>
+        <v>1.439374463918682</v>
       </c>
       <c r="F22">
-        <v>5.078639376223119</v>
+        <v>5.332571345034275</v>
       </c>
       <c r="G22">
         <v>2.19</v>
@@ -3079,28 +3079,28 @@
         <v>1.772</v>
       </c>
       <c r="M22">
-        <v>0.2757701181289154</v>
+        <v>0.2895586240353611</v>
       </c>
       <c r="N22">
-        <v>1.496229881871084</v>
+        <v>1.482441375964638</v>
       </c>
       <c r="O22">
-        <v>0.2184495627531783</v>
+        <v>0.2164364408908372</v>
       </c>
       <c r="P22">
-        <v>1.277780319117906</v>
+        <v>1.266004935073801</v>
       </c>
       <c r="Q22">
-        <v>1.920780319117906</v>
+        <v>1.909004935073801</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1169531838060333</v>
+        <v>0.1177454941930083</v>
       </c>
       <c r="T22">
-        <v>1.643260595982293</v>
+        <v>1.661558757344303</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.425641806381776</v>
+        <v>6.119658863220739</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1027571024124765</v>
+        <v>0.1028650977801265</v>
       </c>
       <c r="C23">
-        <v>20.23941542361882</v>
+        <v>19.95219918766968</v>
       </c>
       <c r="D23">
-        <v>23.38198676865309</v>
+        <v>23.34870250151511</v>
       </c>
       <c r="E23">
-        <v>1.439374463918682</v>
+        <v>1.693306432729837</v>
       </c>
       <c r="F23">
-        <v>5.332571345034275</v>
+        <v>5.58650331384543</v>
       </c>
       <c r="G23">
         <v>2.19</v>
@@ -3161,45 +3161,45 @@
         <v>1.772</v>
       </c>
       <c r="M23">
-        <v>0.2895586240353611</v>
+        <v>0.3089336332556523</v>
       </c>
       <c r="N23">
-        <v>1.482441375964638</v>
+        <v>1.463066366744347</v>
       </c>
       <c r="O23">
-        <v>0.2164364408908372</v>
+        <v>0.2136076895446747</v>
       </c>
       <c r="P23">
-        <v>1.266004935073801</v>
+        <v>1.249458677199673</v>
       </c>
       <c r="Q23">
-        <v>1.909004935073801</v>
+        <v>1.892458677199673</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1177454941930083</v>
+        <v>0.1185581202309314</v>
       </c>
       <c r="T23">
-        <v>1.661558757344303</v>
+        <v>1.68032610233098</v>
       </c>
       <c r="U23">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V23">
         <v>0.146</v>
       </c>
       <c r="W23">
-        <v>0.0463722</v>
+        <v>0.0472262</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.119658863220739</v>
+        <v>5.735859774560751</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1028650977801265</v>
+        <v>0.1027937531477764</v>
       </c>
       <c r="C24">
-        <v>19.95219918766968</v>
+        <v>19.7202450646082</v>
       </c>
       <c r="D24">
-        <v>23.34870250151511</v>
+        <v>23.37068034726479</v>
       </c>
       <c r="E24">
-        <v>1.693306432729837</v>
+        <v>1.947238401540994</v>
       </c>
       <c r="F24">
-        <v>5.58650331384543</v>
+        <v>5.840435282656586</v>
       </c>
       <c r="G24">
         <v>2.19</v>
@@ -3243,28 +3243,28 @@
         <v>1.772</v>
       </c>
       <c r="M24">
-        <v>0.3089336332556523</v>
+        <v>0.3229760711309093</v>
       </c>
       <c r="N24">
-        <v>1.463066366744347</v>
+        <v>1.44902392886909</v>
       </c>
       <c r="O24">
-        <v>0.2136076895446747</v>
+        <v>0.2115574936148872</v>
       </c>
       <c r="P24">
-        <v>1.249458677199673</v>
+        <v>1.237466435254203</v>
       </c>
       <c r="Q24">
-        <v>1.892458677199673</v>
+        <v>1.880466435254203</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1185581202309314</v>
+        <v>0.1193918534386707</v>
       </c>
       <c r="T24">
-        <v>1.68032610233098</v>
+        <v>1.699580910823804</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.735859774560751</v>
+        <v>5.486474566971152</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1027937531477764</v>
+        <v>0.1027224085154263</v>
       </c>
       <c r="C25">
-        <v>19.7202450646082</v>
+        <v>19.48833235547954</v>
       </c>
       <c r="D25">
-        <v>23.37068034726479</v>
+        <v>23.39269960694728</v>
       </c>
       <c r="E25">
-        <v>1.947238401540994</v>
+        <v>2.20117037035215</v>
       </c>
       <c r="F25">
-        <v>5.840435282656586</v>
+        <v>6.094367251467743</v>
       </c>
       <c r="G25">
         <v>2.19</v>
@@ -3325,28 +3325,28 @@
         <v>1.772</v>
       </c>
       <c r="M25">
-        <v>0.3229760711309093</v>
+        <v>0.3370185090061662</v>
       </c>
       <c r="N25">
-        <v>1.44902392886909</v>
+        <v>1.434981490993833</v>
       </c>
       <c r="O25">
-        <v>0.2115574936148872</v>
+        <v>0.2095072976850997</v>
       </c>
       <c r="P25">
-        <v>1.237466435254203</v>
+        <v>1.225474193308734</v>
       </c>
       <c r="Q25">
-        <v>1.880466435254203</v>
+        <v>1.868474193308734</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1193918534386707</v>
+        <v>0.120247526993982</v>
       </c>
       <c r="T25">
-        <v>1.699580910823804</v>
+        <v>1.719342424803281</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.486474566971152</v>
+        <v>5.257871460014021</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1027224085154263</v>
+        <v>0.1026510638830763</v>
       </c>
       <c r="C26">
-        <v>19.48833235547954</v>
+        <v>19.25646117745152</v>
       </c>
       <c r="D26">
-        <v>23.39269960694728</v>
+        <v>23.41476039773042</v>
       </c>
       <c r="E26">
-        <v>2.201170370352149</v>
+        <v>2.455102339163306</v>
       </c>
       <c r="F26">
-        <v>6.094367251467742</v>
+        <v>6.348299220278898</v>
       </c>
       <c r="G26">
         <v>2.19</v>
@@ -3407,28 +3407,28 @@
         <v>1.772</v>
       </c>
       <c r="M26">
-        <v>0.3370185090061661</v>
+        <v>0.3510609468814231</v>
       </c>
       <c r="N26">
-        <v>1.434981490993833</v>
+        <v>1.420939053118576</v>
       </c>
       <c r="O26">
-        <v>0.2095072976850997</v>
+        <v>0.2074571017553122</v>
       </c>
       <c r="P26">
-        <v>1.225474193308734</v>
+        <v>1.213481951363264</v>
       </c>
       <c r="Q26">
-        <v>1.868474193308734</v>
+        <v>1.856481951363264</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.120247526993982</v>
+        <v>0.1211260185107684</v>
       </c>
       <c r="T26">
-        <v>1.719342424803281</v>
+        <v>1.739630912488877</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.257871460014022</v>
+        <v>5.047556601613461</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1026510638830763</v>
+        <v>0.1025797192507262</v>
       </c>
       <c r="C27">
-        <v>19.25646117745152</v>
+        <v>19.02463164813443</v>
       </c>
       <c r="D27">
-        <v>23.41476039773042</v>
+        <v>23.43686283722448</v>
       </c>
       <c r="E27">
-        <v>2.455102339163306</v>
+        <v>2.709034307974462</v>
       </c>
       <c r="F27">
-        <v>6.348299220278898</v>
+        <v>6.602231189090054</v>
       </c>
       <c r="G27">
         <v>2.19</v>
@@ -3489,28 +3489,28 @@
         <v>1.772</v>
       </c>
       <c r="M27">
-        <v>0.3510609468814231</v>
+        <v>0.36510338475668</v>
       </c>
       <c r="N27">
-        <v>1.420939053118576</v>
+        <v>1.40689661524332</v>
       </c>
       <c r="O27">
-        <v>0.2074571017553122</v>
+        <v>0.2054069058255246</v>
       </c>
       <c r="P27">
-        <v>1.213481951363264</v>
+        <v>1.201489709417795</v>
       </c>
       <c r="Q27">
-        <v>1.856481951363264</v>
+        <v>1.844489709417795</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1211260185107684</v>
+        <v>0.1220282530415219</v>
       </c>
       <c r="T27">
-        <v>1.739630912488877</v>
+        <v>1.76046773767949</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.047556601613461</v>
+        <v>4.853419809243713</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1025797192507262</v>
+        <v>0.1025083746183761</v>
       </c>
       <c r="C28">
-        <v>19.02463164813443</v>
+        <v>18.792843885583</v>
       </c>
       <c r="D28">
-        <v>23.43686283722448</v>
+        <v>23.45900704348421</v>
       </c>
       <c r="E28">
-        <v>2.709034307974462</v>
+        <v>2.962966276785618</v>
       </c>
       <c r="F28">
-        <v>6.602231189090054</v>
+        <v>6.856163157901211</v>
       </c>
       <c r="G28">
         <v>2.19</v>
@@ -3571,28 +3571,28 @@
         <v>1.772</v>
       </c>
       <c r="M28">
-        <v>0.36510338475668</v>
+        <v>0.379145822631937</v>
       </c>
       <c r="N28">
-        <v>1.40689661524332</v>
+        <v>1.392854177368063</v>
       </c>
       <c r="O28">
-        <v>0.2054069058255246</v>
+        <v>0.2033567098957371</v>
       </c>
       <c r="P28">
-        <v>1.201489709417795</v>
+        <v>1.189497467472326</v>
       </c>
       <c r="Q28">
-        <v>1.844489709417795</v>
+        <v>1.832497467472326</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1220282530415219</v>
+        <v>0.1229552063265427</v>
       </c>
       <c r="T28">
-        <v>1.76046773767949</v>
+        <v>1.781875434793134</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.853419809243713</v>
+        <v>4.673663520012464</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1025083746183761</v>
+        <v>0.1024370299860261</v>
       </c>
       <c r="C29">
-        <v>18.792843885583</v>
+        <v>18.56109800829858</v>
       </c>
       <c r="D29">
-        <v>23.45900704348421</v>
+        <v>23.48119313501094</v>
       </c>
       <c r="E29">
-        <v>2.962966276785618</v>
+        <v>3.216898245596774</v>
       </c>
       <c r="F29">
-        <v>6.856163157901211</v>
+        <v>7.110095126712366</v>
       </c>
       <c r="G29">
         <v>2.19</v>
@@ -3653,28 +3653,28 @@
         <v>1.772</v>
       </c>
       <c r="M29">
-        <v>0.379145822631937</v>
+        <v>0.3931882605071939</v>
       </c>
       <c r="N29">
-        <v>1.392854177368063</v>
+        <v>1.378811739492806</v>
       </c>
       <c r="O29">
-        <v>0.2033567098957371</v>
+        <v>0.2013065139659496</v>
       </c>
       <c r="P29">
-        <v>1.189497467472326</v>
+        <v>1.177505225526856</v>
       </c>
       <c r="Q29">
-        <v>1.832497467472326</v>
+        <v>1.820505225526856</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1229552063265427</v>
+        <v>0.1239079083139251</v>
       </c>
       <c r="T29">
-        <v>1.781875434793134</v>
+        <v>1.803877790159934</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.673663520012464</v>
+        <v>4.506746965726304</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1024370299860261</v>
+        <v>0.102984835353676</v>
       </c>
       <c r="C30">
-        <v>18.56109800829858</v>
+        <v>18.13788278135153</v>
       </c>
       <c r="D30">
-        <v>23.48119313501094</v>
+        <v>23.31190987687505</v>
       </c>
       <c r="E30">
-        <v>3.216898245596774</v>
+        <v>3.47083021440793</v>
       </c>
       <c r="F30">
-        <v>7.110095126712366</v>
+        <v>7.364027095523523</v>
       </c>
       <c r="G30">
         <v>2.19</v>
@@ -3735,45 +3735,45 @@
         <v>1.772</v>
       </c>
       <c r="M30">
-        <v>0.3931882605071939</v>
+        <v>0.4256407661212596</v>
       </c>
       <c r="N30">
-        <v>1.378811739492806</v>
+        <v>1.34635923387874</v>
       </c>
       <c r="O30">
-        <v>0.2013065139659496</v>
+        <v>0.196568448146296</v>
       </c>
       <c r="P30">
-        <v>1.177505225526856</v>
+        <v>1.149790785732444</v>
       </c>
       <c r="Q30">
-        <v>1.820505225526856</v>
+        <v>1.792790785732444</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1239079083139251</v>
+        <v>0.1248874469770085</v>
       </c>
       <c r="T30">
-        <v>1.803877790159934</v>
+        <v>1.826499930184953</v>
       </c>
       <c r="U30">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V30">
         <v>0.146</v>
       </c>
       <c r="W30">
-        <v>0.0472262</v>
+        <v>0.0493612</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.506746965726304</v>
+        <v>4.16313506844685</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.102984835353676</v>
+        <v>0.1029348407213259</v>
       </c>
       <c r="C31">
-        <v>18.13788278135153</v>
+        <v>17.89929891311484</v>
       </c>
       <c r="D31">
-        <v>23.31190987687505</v>
+        <v>23.32725797744952</v>
       </c>
       <c r="E31">
-        <v>3.470830214407929</v>
+        <v>3.724762183219084</v>
       </c>
       <c r="F31">
-        <v>7.364027095523522</v>
+        <v>7.617959064334677</v>
       </c>
       <c r="G31">
         <v>2.19</v>
@@ -3817,28 +3817,28 @@
         <v>1.772</v>
       </c>
       <c r="M31">
-        <v>0.4256407661212596</v>
+        <v>0.4403180339185443</v>
       </c>
       <c r="N31">
-        <v>1.34635923387874</v>
+        <v>1.331681966081455</v>
       </c>
       <c r="O31">
-        <v>0.196568448146296</v>
+        <v>0.1944255670478924</v>
       </c>
       <c r="P31">
-        <v>1.149790785732444</v>
+        <v>1.137256399033563</v>
       </c>
       <c r="Q31">
-        <v>1.792790785732444</v>
+        <v>1.780256399033563</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1248874469770085</v>
+        <v>0.1258949724590371</v>
       </c>
       <c r="T31">
-        <v>1.826499930184953</v>
+        <v>1.849768417067831</v>
       </c>
       <c r="U31">
         <v>0.0578</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.16313506844685</v>
+        <v>4.024363899498621</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1029348407213259</v>
+        <v>0.1038114360889759</v>
       </c>
       <c r="C32">
-        <v>17.89929891311484</v>
+        <v>17.379152552675</v>
       </c>
       <c r="D32">
-        <v>23.32725797744952</v>
+        <v>23.06104358582083</v>
       </c>
       <c r="E32">
-        <v>3.724762183219084</v>
+        <v>3.978694152030241</v>
       </c>
       <c r="F32">
-        <v>7.617959064334677</v>
+        <v>7.871891033145833</v>
       </c>
       <c r="G32">
         <v>2.19</v>
@@ -3899,45 +3899,45 @@
         <v>1.772</v>
       </c>
       <c r="M32">
-        <v>0.4403180339185443</v>
+        <v>0.4825469203318396</v>
       </c>
       <c r="N32">
-        <v>1.331681966081455</v>
+        <v>1.28945307966816</v>
       </c>
       <c r="O32">
-        <v>0.1944255670478924</v>
+        <v>0.1882601496315514</v>
       </c>
       <c r="P32">
-        <v>1.137256399033563</v>
+        <v>1.101192930036609</v>
       </c>
       <c r="Q32">
-        <v>1.780256399033563</v>
+        <v>1.744192930036609</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1258949724590371</v>
+        <v>0.1269317015782259</v>
       </c>
       <c r="T32">
-        <v>1.849768417067831</v>
+        <v>1.873711352845864</v>
       </c>
       <c r="U32">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V32">
         <v>0.146</v>
       </c>
       <c r="W32">
-        <v>0.0493612</v>
+        <v>0.0523502</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.024363899498621</v>
+        <v>3.672181761685318</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1038114360889759</v>
+        <v>0.1037913314566258</v>
       </c>
       <c r="C33">
-        <v>17.379152552675</v>
+        <v>17.13125808804149</v>
       </c>
       <c r="D33">
-        <v>23.06104358582083</v>
+        <v>23.06708108999848</v>
       </c>
       <c r="E33">
-        <v>3.978694152030241</v>
+        <v>4.232626120841397</v>
       </c>
       <c r="F33">
-        <v>7.871891033145833</v>
+        <v>8.12582300195699</v>
       </c>
       <c r="G33">
         <v>2.19</v>
@@ -3981,28 +3981,28 @@
         <v>1.772</v>
       </c>
       <c r="M33">
-        <v>0.4825469203318396</v>
+        <v>0.4981129500199635</v>
       </c>
       <c r="N33">
-        <v>1.28945307966816</v>
+        <v>1.273887049980036</v>
       </c>
       <c r="O33">
-        <v>0.1882601496315514</v>
+        <v>0.1859875092970853</v>
       </c>
       <c r="P33">
-        <v>1.101192930036609</v>
+        <v>1.087899540682951</v>
       </c>
       <c r="Q33">
-        <v>1.744192930036609</v>
+        <v>1.730899540682951</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1269317015782259</v>
+        <v>0.1279989227303321</v>
       </c>
       <c r="T33">
-        <v>1.873711352845864</v>
+        <v>1.898358492617369</v>
       </c>
       <c r="U33">
         <v>0.0613</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.672181761685318</v>
+        <v>3.557426081632652</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1037913314566258</v>
+        <v>0.1045603228242757</v>
       </c>
       <c r="C34">
-        <v>17.13125808804149</v>
+        <v>16.64862457201701</v>
       </c>
       <c r="D34">
-        <v>23.06708108999848</v>
+        <v>22.83837954278515</v>
       </c>
       <c r="E34">
-        <v>4.232626120841397</v>
+        <v>4.486558089652553</v>
       </c>
       <c r="F34">
-        <v>8.12582300195699</v>
+        <v>8.379754970768145</v>
       </c>
       <c r="G34">
         <v>2.19</v>
@@ -4063,45 +4063,45 @@
         <v>1.772</v>
       </c>
       <c r="M34">
-        <v>0.4981129500199635</v>
+        <v>0.5371422936262381</v>
       </c>
       <c r="N34">
-        <v>1.273887049980036</v>
+        <v>1.234857706373762</v>
       </c>
       <c r="O34">
-        <v>0.1859875092970853</v>
+        <v>0.1802892251305692</v>
       </c>
       <c r="P34">
-        <v>1.087899540682951</v>
+        <v>1.054568481243192</v>
       </c>
       <c r="Q34">
-        <v>1.730899540682951</v>
+        <v>1.697568481243192</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1279989227303321</v>
+        <v>0.1290980012302623</v>
       </c>
       <c r="T34">
-        <v>1.898358492617369</v>
+        <v>1.923741367904441</v>
       </c>
       <c r="U34">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V34">
         <v>0.146</v>
       </c>
       <c r="W34">
-        <v>0.0523502</v>
+        <v>0.0547414</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>3.557426081632652</v>
+        <v>3.298939631130625</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1045603228242757</v>
+        <v>0.1045641301919257</v>
       </c>
       <c r="C35">
-        <v>16.64862457201701</v>
+        <v>16.39357155631388</v>
       </c>
       <c r="D35">
-        <v>22.83837954278515</v>
+        <v>22.83725849589318</v>
       </c>
       <c r="E35">
-        <v>4.486558089652553</v>
+        <v>4.74049005846371</v>
       </c>
       <c r="F35">
-        <v>8.379754970768145</v>
+        <v>8.633686939579302</v>
       </c>
       <c r="G35">
         <v>2.19</v>
@@ -4145,28 +4145,28 @@
         <v>1.772</v>
       </c>
       <c r="M35">
-        <v>0.5371422936262381</v>
+        <v>0.5534193328270333</v>
       </c>
       <c r="N35">
-        <v>1.234857706373762</v>
+        <v>1.218580667172966</v>
       </c>
       <c r="O35">
-        <v>0.1802892251305692</v>
+        <v>0.1779127774072531</v>
       </c>
       <c r="P35">
-        <v>1.054568481243192</v>
+        <v>1.040667889765713</v>
       </c>
       <c r="Q35">
-        <v>1.697568481243192</v>
+        <v>1.683667889765713</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1290980012302623</v>
+        <v>0.1302303851392813</v>
       </c>
       <c r="T35">
-        <v>1.923741367904441</v>
+        <v>1.949893421230516</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.298939631130625</v>
+        <v>3.2019119949209</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1045641301919257</v>
+        <v>0.1045679375595756</v>
       </c>
       <c r="C36">
-        <v>16.39357155631388</v>
+        <v>16.13851865066099</v>
       </c>
       <c r="D36">
-        <v>22.83725849589318</v>
+        <v>22.83613755905144</v>
       </c>
       <c r="E36">
-        <v>4.74049005846371</v>
+        <v>4.994422027274865</v>
       </c>
       <c r="F36">
-        <v>8.633686939579302</v>
+        <v>8.887618908390458</v>
       </c>
       <c r="G36">
         <v>2.19</v>
@@ -4227,28 +4227,28 @@
         <v>1.772</v>
       </c>
       <c r="M36">
-        <v>0.5534193328270333</v>
+        <v>0.5696963720278284</v>
       </c>
       <c r="N36">
-        <v>1.218580667172966</v>
+        <v>1.202303627972171</v>
       </c>
       <c r="O36">
-        <v>0.1779127774072531</v>
+        <v>0.175536329683937</v>
       </c>
       <c r="P36">
-        <v>1.040667889765713</v>
+        <v>1.026767298288234</v>
       </c>
       <c r="Q36">
-        <v>1.683667889765713</v>
+        <v>1.669767298288234</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1302303851392813</v>
+        <v>0.1313976116301163</v>
       </c>
       <c r="T36">
-        <v>1.949893421230516</v>
+        <v>1.976850153120469</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.2019119949209</v>
+        <v>3.110428795066017</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1045679375595756</v>
+        <v>0.1045717449272255</v>
       </c>
       <c r="C37">
-        <v>16.13851865066099</v>
+        <v>15.88346585504212</v>
       </c>
       <c r="D37">
-        <v>22.83613755905144</v>
+        <v>22.83501673224373</v>
       </c>
       <c r="E37">
-        <v>4.994422027274865</v>
+        <v>5.248353996086022</v>
       </c>
       <c r="F37">
-        <v>8.887618908390458</v>
+        <v>9.141550877201615</v>
       </c>
       <c r="G37">
         <v>2.19</v>
@@ -4309,28 +4309,28 @@
         <v>1.772</v>
       </c>
       <c r="M37">
-        <v>0.5696963720278284</v>
+        <v>0.5859734112286236</v>
       </c>
       <c r="N37">
-        <v>1.202303627972171</v>
+        <v>1.186026588771376</v>
       </c>
       <c r="O37">
-        <v>0.175536329683937</v>
+        <v>0.1731598819606209</v>
       </c>
       <c r="P37">
-        <v>1.026767298288234</v>
+        <v>1.012866706810755</v>
       </c>
       <c r="Q37">
-        <v>1.669767298288234</v>
+        <v>1.655866706810755</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1313976116301163</v>
+        <v>0.1326013139487899</v>
       </c>
       <c r="T37">
-        <v>1.976850153120469</v>
+        <v>2.004649282881984</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.110428795066017</v>
+        <v>3.024027995203072</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1045717449272255</v>
+        <v>0.1070401962948754</v>
       </c>
       <c r="C38">
-        <v>15.88346585504211</v>
+        <v>14.92530710744637</v>
       </c>
       <c r="D38">
-        <v>22.83501673224373</v>
+        <v>22.13078995345914</v>
       </c>
       <c r="E38">
-        <v>5.248353996086021</v>
+        <v>5.502285964897176</v>
       </c>
       <c r="F38">
-        <v>9.141550877201613</v>
+        <v>9.395482846012769</v>
       </c>
       <c r="G38">
         <v>2.19</v>
@@ -4391,45 +4391,45 @@
         <v>1.772</v>
       </c>
       <c r="M38">
-        <v>0.5859734112286235</v>
+        <v>0.6755352166283182</v>
       </c>
       <c r="N38">
-        <v>1.186026588771376</v>
+        <v>1.096464783371681</v>
       </c>
       <c r="O38">
-        <v>0.1731598819606209</v>
+        <v>0.1600838583722655</v>
       </c>
       <c r="P38">
-        <v>1.012866706810755</v>
+        <v>0.9363809249994159</v>
       </c>
       <c r="Q38">
-        <v>1.655866706810755</v>
+        <v>1.579380924999416</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1326013139487899</v>
+        <v>0.1338432290394848</v>
       </c>
       <c r="T38">
-        <v>2.004649282881984</v>
+        <v>2.03333092469942</v>
       </c>
       <c r="U38">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V38">
         <v>0.146</v>
       </c>
       <c r="W38">
-        <v>0.0547414</v>
+        <v>0.0614026</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.024027995203072</v>
+        <v>2.623105289527726</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1070401962948754</v>
+        <v>0.1071106156625254</v>
       </c>
       <c r="C39">
-        <v>14.92530710744637</v>
+        <v>14.65192181807593</v>
       </c>
       <c r="D39">
-        <v>22.13078995345914</v>
+        <v>22.11133663289986</v>
       </c>
       <c r="E39">
-        <v>5.502285964897176</v>
+        <v>5.756217933708333</v>
       </c>
       <c r="F39">
-        <v>9.395482846012769</v>
+        <v>9.649414814823926</v>
       </c>
       <c r="G39">
         <v>2.19</v>
@@ -4473,28 +4473,28 @@
         <v>1.772</v>
       </c>
       <c r="M39">
-        <v>0.6755352166283182</v>
+        <v>0.6937929251858403</v>
       </c>
       <c r="N39">
-        <v>1.096464783371681</v>
+        <v>1.078207074814159</v>
       </c>
       <c r="O39">
-        <v>0.1600838583722655</v>
+        <v>0.1574182329228672</v>
       </c>
       <c r="P39">
-        <v>0.9363809249994159</v>
+        <v>0.920788841891292</v>
       </c>
       <c r="Q39">
-        <v>1.579380924999416</v>
+        <v>1.563788841891292</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1338432290394848</v>
+        <v>0.135125205907299</v>
       </c>
       <c r="T39">
-        <v>2.03333092469942</v>
+        <v>2.062937780769031</v>
       </c>
       <c r="U39">
         <v>0.07190000000000001</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.623105289527726</v>
+        <v>2.554076202961206</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1071106156625254</v>
+        <v>0.1084799690301753</v>
       </c>
       <c r="C40">
-        <v>14.65192181807593</v>
+        <v>14.02639084736477</v>
       </c>
       <c r="D40">
-        <v>22.11133663289986</v>
+        <v>21.73973763099985</v>
       </c>
       <c r="E40">
-        <v>5.756217933708333</v>
+        <v>6.010149902519489</v>
       </c>
       <c r="F40">
-        <v>9.649414814823926</v>
+        <v>9.903346783635081</v>
       </c>
       <c r="G40">
         <v>2.19</v>
@@ -4555,45 +4555,45 @@
         <v>1.772</v>
       </c>
       <c r="M40">
-        <v>0.6937929251858403</v>
+        <v>0.7506736861995392</v>
       </c>
       <c r="N40">
-        <v>1.078207074814159</v>
+        <v>1.02132631380046</v>
       </c>
       <c r="O40">
-        <v>0.1574182329228672</v>
+        <v>0.1491136418148672</v>
       </c>
       <c r="P40">
-        <v>0.920788841891292</v>
+        <v>0.8722126719855933</v>
       </c>
       <c r="Q40">
-        <v>1.563788841891292</v>
+        <v>1.515212671985593</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.135125205907299</v>
+        <v>0.1364492148035661</v>
       </c>
       <c r="T40">
-        <v>2.062937780769031</v>
+        <v>2.093515353431088</v>
       </c>
       <c r="U40">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V40">
         <v>0.146</v>
       </c>
       <c r="W40">
-        <v>0.0614026</v>
+        <v>0.0647332</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.554076202961206</v>
+        <v>2.36054631003674</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1084799690301753</v>
+        <v>0.1085836943978252</v>
       </c>
       <c r="C41">
-        <v>14.02639084736477</v>
+        <v>13.74481934030482</v>
       </c>
       <c r="D41">
-        <v>21.73973763099985</v>
+        <v>21.71209809275105</v>
       </c>
       <c r="E41">
-        <v>6.010149902519489</v>
+        <v>6.264081871330646</v>
       </c>
       <c r="F41">
-        <v>9.903346783635081</v>
+        <v>10.15727875244624</v>
       </c>
       <c r="G41">
         <v>2.19</v>
@@ -4637,28 +4637,28 @@
         <v>1.772</v>
       </c>
       <c r="M41">
-        <v>0.7506736861995392</v>
+        <v>0.7699217294354249</v>
       </c>
       <c r="N41">
-        <v>1.02132631380046</v>
+        <v>1.002078270564575</v>
       </c>
       <c r="O41">
-        <v>0.1491136418148672</v>
+        <v>0.1463034275024279</v>
       </c>
       <c r="P41">
-        <v>0.8722126719855933</v>
+        <v>0.8557748430621468</v>
       </c>
       <c r="Q41">
-        <v>1.515212671985593</v>
+        <v>1.498774843062147</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1364492148035661</v>
+        <v>0.1378173573297087</v>
       </c>
       <c r="T41">
-        <v>2.093515353431088</v>
+        <v>2.125112178515214</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.36054631003674</v>
+        <v>2.301532652285821</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1085836943978252</v>
+        <v>0.1086874197654752</v>
       </c>
       <c r="C42">
-        <v>13.74481934030482</v>
+        <v>13.46331802489622</v>
       </c>
       <c r="D42">
-        <v>21.71209809275105</v>
+        <v>21.68452874615361</v>
       </c>
       <c r="E42">
-        <v>6.264081871330646</v>
+        <v>6.518013840141801</v>
       </c>
       <c r="F42">
-        <v>10.15727875244624</v>
+        <v>10.41121072125739</v>
       </c>
       <c r="G42">
         <v>2.19</v>
@@ -4719,28 +4719,28 @@
         <v>1.772</v>
       </c>
       <c r="M42">
-        <v>0.7699217294354249</v>
+        <v>0.7891697726713105</v>
       </c>
       <c r="N42">
-        <v>1.002078270564575</v>
+        <v>0.9828302273286891</v>
       </c>
       <c r="O42">
-        <v>0.1463034275024279</v>
+        <v>0.1434932131899886</v>
       </c>
       <c r="P42">
-        <v>0.8557748430621468</v>
+        <v>0.8393370141387004</v>
       </c>
       <c r="Q42">
-        <v>1.498774843062147</v>
+        <v>1.4823370141387</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1378173573297087</v>
+        <v>0.139231877568602</v>
       </c>
       <c r="T42">
-        <v>2.125112178515214</v>
+        <v>2.157780082415751</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.301532652285821</v>
+        <v>2.245397709547142</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1086874197654752</v>
+        <v>0.1087911451331251</v>
       </c>
       <c r="C43">
-        <v>13.46331802489622</v>
+        <v>13.18188663409654</v>
       </c>
       <c r="D43">
-        <v>21.68452874615361</v>
+        <v>21.65702932416508</v>
       </c>
       <c r="E43">
-        <v>6.518013840141801</v>
+        <v>6.771945808952957</v>
       </c>
       <c r="F43">
-        <v>10.41121072125739</v>
+        <v>10.66514269006855</v>
       </c>
       <c r="G43">
         <v>2.19</v>
@@ -4801,28 +4801,28 @@
         <v>1.772</v>
       </c>
       <c r="M43">
-        <v>0.7891697726713105</v>
+        <v>0.8084178159071961</v>
       </c>
       <c r="N43">
-        <v>0.9828302273286891</v>
+        <v>0.9635821840928035</v>
       </c>
       <c r="O43">
-        <v>0.1434932131899886</v>
+        <v>0.1406829988775493</v>
       </c>
       <c r="P43">
-        <v>0.8393370141387004</v>
+        <v>0.8228991852152542</v>
       </c>
       <c r="Q43">
-        <v>1.4823370141387</v>
+        <v>1.465899185215254</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.139231877568602</v>
+        <v>0.1406951743674571</v>
       </c>
       <c r="T43">
-        <v>2.157780082415751</v>
+        <v>2.191574465761134</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.245397709547142</v>
+        <v>2.191935859319829</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1087911451331251</v>
+        <v>0.1088948705007751</v>
       </c>
       <c r="C44">
-        <v>13.18188663409653</v>
+        <v>12.90052490221621</v>
       </c>
       <c r="D44">
-        <v>21.65702932416508</v>
+        <v>21.62959956109591</v>
       </c>
       <c r="E44">
-        <v>6.771945808952957</v>
+        <v>7.025877777764112</v>
       </c>
       <c r="F44">
-        <v>10.66514269006855</v>
+        <v>10.9190746588797</v>
       </c>
       <c r="G44">
         <v>2.19</v>
@@ -4883,28 +4883,28 @@
         <v>1.772</v>
       </c>
       <c r="M44">
-        <v>0.8084178159071961</v>
+        <v>0.8276658591430817</v>
       </c>
       <c r="N44">
-        <v>0.9635821840928035</v>
+        <v>0.9443341408569179</v>
       </c>
       <c r="O44">
-        <v>0.1406829988775493</v>
+        <v>0.13787278456511</v>
       </c>
       <c r="P44">
-        <v>0.8228991852152542</v>
+        <v>0.8064613562918079</v>
       </c>
       <c r="Q44">
-        <v>1.465899185215254</v>
+        <v>1.449461356291808</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1406951743674571</v>
+        <v>0.1422098149136404</v>
       </c>
       <c r="T44">
-        <v>2.191574465761134</v>
+        <v>2.226554616943198</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.191935859319829</v>
+        <v>2.140960606777508</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1088948705007751</v>
+        <v>0.108998595868425</v>
       </c>
       <c r="C45">
-        <v>12.90052490221621</v>
+        <v>12.61923256491004</v>
       </c>
       <c r="D45">
-        <v>21.62959956109591</v>
+        <v>21.6022391926009</v>
       </c>
       <c r="E45">
-        <v>7.025877777764112</v>
+        <v>7.279809746575268</v>
       </c>
       <c r="F45">
-        <v>10.9190746588797</v>
+        <v>11.17300662769086</v>
       </c>
       <c r="G45">
         <v>2.19</v>
@@ -4965,28 +4965,28 @@
         <v>1.772</v>
       </c>
       <c r="M45">
-        <v>0.8276658591430817</v>
+        <v>0.8469139023789672</v>
       </c>
       <c r="N45">
-        <v>0.9443341408569179</v>
+        <v>0.9250860976210323</v>
       </c>
       <c r="O45">
-        <v>0.13787278456511</v>
+        <v>0.1350625702526707</v>
       </c>
       <c r="P45">
-        <v>0.8064613562918079</v>
+        <v>0.7900235273683616</v>
       </c>
       <c r="Q45">
-        <v>1.449461356291808</v>
+        <v>1.433023527368362</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1422098149136404</v>
+        <v>0.1437785497650446</v>
       </c>
       <c r="T45">
-        <v>2.226554616943198</v>
+        <v>2.262784059238906</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.140960606777508</v>
+        <v>2.092302411168928</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.108998595868425</v>
+        <v>0.1091023212360749</v>
       </c>
       <c r="C46">
-        <v>12.61923256491004</v>
+        <v>12.33800935916866</v>
       </c>
       <c r="D46">
-        <v>21.6022391926009</v>
+        <v>21.57494795567067</v>
       </c>
       <c r="E46">
-        <v>7.279809746575268</v>
+        <v>7.533741715386425</v>
       </c>
       <c r="F46">
-        <v>11.17300662769086</v>
+        <v>11.42693859650202</v>
       </c>
       <c r="G46">
         <v>2.19</v>
@@ -5047,28 +5047,28 @@
         <v>1.772</v>
       </c>
       <c r="M46">
-        <v>0.8469139023789672</v>
+        <v>0.8661619456148529</v>
       </c>
       <c r="N46">
-        <v>0.9250860976210323</v>
+        <v>0.9058380543851466</v>
       </c>
       <c r="O46">
-        <v>0.1350625702526707</v>
+        <v>0.1322523559402314</v>
       </c>
       <c r="P46">
-        <v>0.7900235273683616</v>
+        <v>0.7735856984449152</v>
       </c>
       <c r="Q46">
-        <v>1.433023527368362</v>
+        <v>1.416585698444915</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1437785497650446</v>
+        <v>0.1454043295201362</v>
       </c>
       <c r="T46">
-        <v>2.262784059238906</v>
+        <v>2.300330935799912</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.092302411168928</v>
+        <v>2.045806802031841</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1091023212360749</v>
+        <v>0.1092060466037248</v>
       </c>
       <c r="C47">
-        <v>12.33800935916866</v>
+        <v>12.0568550233101</v>
       </c>
       <c r="D47">
-        <v>21.57494795567067</v>
+        <v>21.54772558862328</v>
       </c>
       <c r="E47">
-        <v>7.533741715386425</v>
+        <v>7.78767368419758</v>
       </c>
       <c r="F47">
-        <v>11.42693859650202</v>
+        <v>11.68087056531317</v>
       </c>
       <c r="G47">
         <v>2.19</v>
@@ -5129,28 +5129,28 @@
         <v>1.772</v>
       </c>
       <c r="M47">
-        <v>0.8661619456148529</v>
+        <v>0.8854099888507385</v>
       </c>
       <c r="N47">
-        <v>0.9058380543851466</v>
+        <v>0.8865900111492611</v>
       </c>
       <c r="O47">
-        <v>0.1322523559402314</v>
+        <v>0.1294421416277921</v>
       </c>
       <c r="P47">
-        <v>0.7735856984449152</v>
+        <v>0.757147869521469</v>
       </c>
       <c r="Q47">
-        <v>1.416585698444915</v>
+        <v>1.400147869521469</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1454043295201362</v>
+        <v>0.1470903233402311</v>
       </c>
       <c r="T47">
-        <v>2.300330935799912</v>
+        <v>2.339268437418734</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.045806802031841</v>
+        <v>2.001332741118105</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1092060466037248</v>
+        <v>0.1150093679713748</v>
       </c>
       <c r="C48">
-        <v>12.0568550233101</v>
+        <v>10.38208559214075</v>
       </c>
       <c r="D48">
-        <v>21.54772558862328</v>
+        <v>20.12688812626508</v>
       </c>
       <c r="E48">
-        <v>7.78767368419758</v>
+        <v>8.041605653008737</v>
       </c>
       <c r="F48">
-        <v>11.68087056531317</v>
+        <v>11.93480253412433</v>
       </c>
       <c r="G48">
         <v>2.19</v>
@@ -5211,45 +5211,45 @@
         <v>1.772</v>
       </c>
       <c r="M48">
-        <v>0.8854099888507385</v>
+        <v>1.07413222807119</v>
       </c>
       <c r="N48">
-        <v>0.8865900111492611</v>
+        <v>0.69786777192881</v>
       </c>
       <c r="O48">
-        <v>0.1294421416277921</v>
+        <v>0.1018886947016062</v>
       </c>
       <c r="P48">
-        <v>0.757147869521469</v>
+        <v>0.5959790772272038</v>
       </c>
       <c r="Q48">
-        <v>1.400147869521469</v>
+        <v>1.238979077227204</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1470903233402311</v>
+        <v>0.1488399395686316</v>
       </c>
       <c r="T48">
-        <v>2.339268437418734</v>
+        <v>2.379675278721285</v>
       </c>
       <c r="U48">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V48">
         <v>0.146</v>
       </c>
       <c r="W48">
-        <v>0.0647332</v>
+        <v>0.07686</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.001332741118105</v>
+        <v>1.649703782915038</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1150093679713748</v>
+        <v>0.1152343613390247</v>
       </c>
       <c r="C49">
-        <v>10.38208559214075</v>
+        <v>10.07683158947143</v>
       </c>
       <c r="D49">
-        <v>20.12688812626508</v>
+        <v>20.07556609240691</v>
       </c>
       <c r="E49">
-        <v>8.041605653008737</v>
+        <v>8.295537621819893</v>
       </c>
       <c r="F49">
-        <v>11.93480253412433</v>
+        <v>12.18873450293549</v>
       </c>
       <c r="G49">
         <v>2.19</v>
@@ -5293,28 +5293,28 @@
         <v>1.772</v>
       </c>
       <c r="M49">
-        <v>1.07413222807119</v>
+        <v>1.096986105264194</v>
       </c>
       <c r="N49">
-        <v>0.69786777192881</v>
+        <v>0.675013894735806</v>
       </c>
       <c r="O49">
-        <v>0.1018886947016062</v>
+        <v>0.09855202863142766</v>
       </c>
       <c r="P49">
-        <v>0.5959790772272038</v>
+        <v>0.5764618661043783</v>
       </c>
       <c r="Q49">
-        <v>1.238979077227204</v>
+        <v>1.219461866104378</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1488399395686316</v>
+        <v>0.1506568487288936</v>
       </c>
       <c r="T49">
-        <v>2.379675278721285</v>
+        <v>2.421636229304704</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.649703782915038</v>
+        <v>1.615334954104308</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1152343613390247</v>
+        <v>0.1154593547066746</v>
       </c>
       <c r="C50">
-        <v>10.07683158947144</v>
+        <v>9.771838655661877</v>
       </c>
       <c r="D50">
-        <v>20.07556609240692</v>
+        <v>20.02450512740852</v>
       </c>
       <c r="E50">
-        <v>8.295537621819891</v>
+        <v>8.549469590631048</v>
       </c>
       <c r="F50">
-        <v>12.18873450293548</v>
+        <v>12.44266647174664</v>
       </c>
       <c r="G50">
         <v>2.19</v>
@@ -5375,28 +5375,28 @@
         <v>1.772</v>
       </c>
       <c r="M50">
-        <v>1.096986105264193</v>
+        <v>1.119839982457198</v>
       </c>
       <c r="N50">
-        <v>0.6750138947358062</v>
+        <v>0.652160017542802</v>
       </c>
       <c r="O50">
-        <v>0.0985520286314277</v>
+        <v>0.09521536256124907</v>
       </c>
       <c r="P50">
-        <v>0.5764618661043786</v>
+        <v>0.5569446549815529</v>
       </c>
       <c r="Q50">
-        <v>1.219461866104379</v>
+        <v>1.199944654981553</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1506568487288936</v>
+        <v>0.1525450092287738</v>
       </c>
       <c r="T50">
-        <v>2.421636229304704</v>
+        <v>2.465242707361982</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.615334954104308</v>
+        <v>1.582368934632791</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1154593547066746</v>
+        <v>0.1156843480743246</v>
       </c>
       <c r="C51">
-        <v>9.771838655661877</v>
+        <v>9.467104803728205</v>
       </c>
       <c r="D51">
-        <v>20.02450512740852</v>
+        <v>19.973703244286</v>
       </c>
       <c r="E51">
-        <v>8.549469590631048</v>
+        <v>8.803401559442204</v>
       </c>
       <c r="F51">
-        <v>12.44266647174664</v>
+        <v>12.6965984405578</v>
       </c>
       <c r="G51">
         <v>2.19</v>
@@ -5457,28 +5457,28 @@
         <v>1.772</v>
       </c>
       <c r="M51">
-        <v>1.119839982457198</v>
+        <v>1.142693859650202</v>
       </c>
       <c r="N51">
-        <v>0.652160017542802</v>
+        <v>0.6293061403497979</v>
       </c>
       <c r="O51">
-        <v>0.09521536256124907</v>
+        <v>0.09187869649107049</v>
       </c>
       <c r="P51">
-        <v>0.5569446549815529</v>
+        <v>0.5374274438587274</v>
       </c>
       <c r="Q51">
-        <v>1.199944654981553</v>
+        <v>1.180427443858727</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1525450092287738</v>
+        <v>0.1545086961486491</v>
       </c>
       <c r="T51">
-        <v>2.465242707361982</v>
+        <v>2.510593444541551</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.582368934632791</v>
+        <v>1.550721555940135</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1156843480743246</v>
+        <v>0.1159093414419745</v>
       </c>
       <c r="C52">
-        <v>9.467104803728205</v>
+        <v>9.162628066799293</v>
       </c>
       <c r="D52">
-        <v>19.973703244286</v>
+        <v>19.92315847616824</v>
       </c>
       <c r="E52">
-        <v>8.803401559442204</v>
+        <v>9.057333528253359</v>
       </c>
       <c r="F52">
-        <v>12.6965984405578</v>
+        <v>12.95053040936895</v>
       </c>
       <c r="G52">
         <v>2.19</v>
@@ -5539,28 +5539,28 @@
         <v>1.772</v>
       </c>
       <c r="M52">
-        <v>1.142693859650202</v>
+        <v>1.165547736843206</v>
       </c>
       <c r="N52">
-        <v>0.6293061403497979</v>
+        <v>0.6064522631567939</v>
       </c>
       <c r="O52">
-        <v>0.09187869649107049</v>
+        <v>0.0885420304208919</v>
       </c>
       <c r="P52">
-        <v>0.5374274438587274</v>
+        <v>0.517910232735902</v>
       </c>
       <c r="Q52">
-        <v>1.180427443858727</v>
+        <v>1.160910232735902</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1545086961486491</v>
+        <v>0.15655253355505</v>
       </c>
       <c r="T52">
-        <v>2.510593444541551</v>
+        <v>2.557795232218245</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.550721555940135</v>
+        <v>1.520315250921701</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1159093414419745</v>
+        <v>0.1426970642360239</v>
       </c>
       <c r="C53">
-        <v>9.162628066799293</v>
+        <v>4.295859942531285</v>
       </c>
       <c r="D53">
-        <v>19.92315847616824</v>
+        <v>15.31032232071139</v>
       </c>
       <c r="E53">
-        <v>9.057333528253359</v>
+        <v>9.311265497064516</v>
       </c>
       <c r="F53">
-        <v>12.95053040936895</v>
+        <v>13.20446237818011</v>
       </c>
       <c r="G53">
         <v>2.19</v>
@@ -5621,45 +5621,45 @@
         <v>1.772</v>
       </c>
       <c r="M53">
-        <v>1.165547736843206</v>
+        <v>1.93841507711684</v>
       </c>
       <c r="N53">
-        <v>0.6064522631567939</v>
+        <v>-0.1664150771168407</v>
       </c>
       <c r="O53">
-        <v>0.0885420304208919</v>
+        <v>-0.02429660125905874</v>
       </c>
       <c r="P53">
-        <v>0.517910232735902</v>
+        <v>-0.1421184758577819</v>
       </c>
       <c r="Q53">
-        <v>1.160910232735902</v>
+        <v>0.5008815241422181</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.15655253355505</v>
+        <v>0.1594777184553137</v>
       </c>
       <c r="T53">
-        <v>2.557795232218245</v>
+        <v>2.625351465480688</v>
       </c>
       <c r="U53">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.146</v>
+        <v>0.1334657386099178</v>
       </c>
       <c r="W53">
-        <v>0.07686</v>
+        <v>0.1272072295720641</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y53">
-        <v>1.520315250921701</v>
+        <v>0.9141488945884784</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1426970642360239</v>
+        <v>0.1437070642360239</v>
       </c>
       <c r="C54">
-        <v>4.295859942531285</v>
+        <v>3.909431299621746</v>
       </c>
       <c r="D54">
-        <v>15.31032232071139</v>
+        <v>15.17782564661301</v>
       </c>
       <c r="E54">
-        <v>9.311265497064516</v>
+        <v>9.565197465875672</v>
       </c>
       <c r="F54">
-        <v>13.20446237818011</v>
+        <v>13.45839434699126</v>
       </c>
       <c r="G54">
         <v>2.19</v>
@@ -5703,37 +5703,37 @@
         <v>1.772</v>
       </c>
       <c r="M54">
-        <v>1.93841507711684</v>
+        <v>1.975692290138318</v>
       </c>
       <c r="N54">
-        <v>-0.1664150771168407</v>
+        <v>-0.2036922901383182</v>
       </c>
       <c r="O54">
-        <v>-0.02429660125905874</v>
+        <v>-0.02973907436019446</v>
       </c>
       <c r="P54">
-        <v>-0.1421184758577819</v>
+        <v>-0.1739532157781238</v>
       </c>
       <c r="Q54">
-        <v>0.5008815241422181</v>
+        <v>0.4690467842218762</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1594777184553137</v>
+        <v>0.1618963933160651</v>
       </c>
       <c r="T54">
-        <v>2.625351465480688</v>
+        <v>2.681210007299426</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.1334657386099178</v>
+        <v>0.1309475171267118</v>
       </c>
       <c r="W54">
-        <v>0.1272072295720641</v>
+        <v>0.1275769044857987</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.9141488945884784</v>
+        <v>0.8969008022377525</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1437070642360239</v>
+        <v>0.1447170642360239</v>
       </c>
       <c r="C55">
-        <v>3.909431299621746</v>
+        <v>3.525276253087718</v>
       </c>
       <c r="D55">
-        <v>15.17782564661301</v>
+        <v>15.04760256889014</v>
       </c>
       <c r="E55">
-        <v>9.565197465875672</v>
+        <v>9.819129434686829</v>
       </c>
       <c r="F55">
-        <v>13.45839434699126</v>
+        <v>13.71232631580242</v>
       </c>
       <c r="G55">
         <v>2.19</v>
@@ -5785,37 +5785,37 @@
         <v>1.772</v>
       </c>
       <c r="M55">
-        <v>1.975692290138318</v>
+        <v>2.012969503159796</v>
       </c>
       <c r="N55">
-        <v>-0.2036922901383182</v>
+        <v>-0.240969503159796</v>
       </c>
       <c r="O55">
-        <v>-0.02973907436019446</v>
+        <v>-0.03518154746133022</v>
       </c>
       <c r="P55">
-        <v>-0.1739532157781238</v>
+        <v>-0.2057879556984658</v>
       </c>
       <c r="Q55">
-        <v>0.4690467842218762</v>
+        <v>0.4372120443015342</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1618963933160651</v>
+        <v>0.1644202279533709</v>
       </c>
       <c r="T55">
-        <v>2.681210007299426</v>
+        <v>2.739497181371152</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.1309475171267118</v>
+        <v>0.1285225631058468</v>
       </c>
       <c r="W55">
-        <v>0.1275769044857987</v>
+        <v>0.1279328877360617</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8969008022377525</v>
+        <v>0.8802915281222384</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1447170642360239</v>
+        <v>0.1457270642360239</v>
       </c>
       <c r="C56">
-        <v>3.525276253087718</v>
+        <v>3.143336779586807</v>
       </c>
       <c r="D56">
-        <v>15.04760256889014</v>
+        <v>14.91959506420038</v>
       </c>
       <c r="E56">
-        <v>9.819129434686829</v>
+        <v>10.07306140349798</v>
       </c>
       <c r="F56">
-        <v>13.71232631580242</v>
+        <v>13.96625828461358</v>
       </c>
       <c r="G56">
         <v>2.19</v>
@@ -5867,37 +5867,37 @@
         <v>1.772</v>
       </c>
       <c r="M56">
-        <v>2.012969503159796</v>
+        <v>2.050246716181273</v>
       </c>
       <c r="N56">
-        <v>-0.240969503159796</v>
+        <v>-0.2782467161812738</v>
       </c>
       <c r="O56">
-        <v>-0.03518154746133022</v>
+        <v>-0.04062402056246598</v>
       </c>
       <c r="P56">
-        <v>-0.2057879556984658</v>
+        <v>-0.2376226956188079</v>
       </c>
       <c r="Q56">
-        <v>0.4372120443015342</v>
+        <v>0.4053773043811921</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1644202279533709</v>
+        <v>0.1670562330190013</v>
       </c>
       <c r="T56">
-        <v>2.739497181371152</v>
+        <v>2.800374896512734</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.1285225631058468</v>
+        <v>0.126185789231195</v>
       </c>
       <c r="W56">
-        <v>0.1279328877360617</v>
+        <v>0.1282759261408606</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8802915281222384</v>
+        <v>0.864286227610925</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1457270642360239</v>
+        <v>0.1467370642360239</v>
       </c>
       <c r="C57">
-        <v>3.143336779586807</v>
+        <v>2.763556813503047</v>
       </c>
       <c r="D57">
-        <v>14.91959506420038</v>
+        <v>14.79374706692778</v>
       </c>
       <c r="E57">
-        <v>10.07306140349798</v>
+        <v>10.32699337230914</v>
       </c>
       <c r="F57">
-        <v>13.96625828461358</v>
+        <v>14.22019025342473</v>
       </c>
       <c r="G57">
         <v>2.19</v>
@@ -5949,37 +5949,37 @@
         <v>1.772</v>
       </c>
       <c r="M57">
-        <v>2.050246716181273</v>
+        <v>2.087523929202751</v>
       </c>
       <c r="N57">
-        <v>-0.2782467161812738</v>
+        <v>-0.3155239292027512</v>
       </c>
       <c r="O57">
-        <v>-0.04062402056246598</v>
+        <v>-0.04606649366360167</v>
       </c>
       <c r="P57">
-        <v>-0.2376226956188079</v>
+        <v>-0.2694574355391495</v>
       </c>
       <c r="Q57">
-        <v>0.4053773043811921</v>
+        <v>0.3735425644608505</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1670562330190013</v>
+        <v>0.1698120564967059</v>
       </c>
       <c r="T57">
-        <v>2.800374896512734</v>
+        <v>2.864019780524387</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.126185789231195</v>
+        <v>0.1239324715663523</v>
       </c>
       <c r="W57">
-        <v>0.1282759261408606</v>
+        <v>0.1286067131740595</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.864286227610925</v>
+        <v>0.8488525449750157</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1467370642360239</v>
+        <v>0.1477470642360239</v>
       </c>
       <c r="C58">
-        <v>2.763556813503047</v>
+        <v>2.385882165069669</v>
       </c>
       <c r="D58">
-        <v>14.79374706692778</v>
+        <v>14.67000438730556</v>
       </c>
       <c r="E58">
-        <v>10.32699337230914</v>
+        <v>10.5809253411203</v>
       </c>
       <c r="F58">
-        <v>14.22019025342473</v>
+        <v>14.47412222223589</v>
       </c>
       <c r="G58">
         <v>2.19</v>
@@ -6031,37 +6031,37 @@
         <v>1.772</v>
       </c>
       <c r="M58">
-        <v>2.087523929202751</v>
+        <v>2.124801142224229</v>
       </c>
       <c r="N58">
-        <v>-0.3155239292027512</v>
+        <v>-0.3528011422242294</v>
       </c>
       <c r="O58">
-        <v>-0.04606649366360167</v>
+        <v>-0.05150896676473749</v>
       </c>
       <c r="P58">
-        <v>-0.2694574355391495</v>
+        <v>-0.3012921754594919</v>
       </c>
       <c r="Q58">
-        <v>0.3735425644608505</v>
+        <v>0.3417078245405081</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1698120564967059</v>
+        <v>0.1726960578105828</v>
       </c>
       <c r="T58">
-        <v>2.864019780524387</v>
+        <v>2.930624891699373</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.1239324715663523</v>
+        <v>0.1217582176792233</v>
       </c>
       <c r="W58">
-        <v>0.1286067131740595</v>
+        <v>0.12892589364469</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8488525449750157</v>
+        <v>0.8339603950631731</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1477470642360239</v>
+        <v>0.1487570642360239</v>
       </c>
       <c r="C59">
-        <v>2.385882165069669</v>
+        <v>2.01026044256689</v>
       </c>
       <c r="D59">
-        <v>14.67000438730556</v>
+        <v>14.54831463361393</v>
       </c>
       <c r="E59">
-        <v>10.5809253411203</v>
+        <v>10.83485730993145</v>
       </c>
       <c r="F59">
-        <v>14.47412222223589</v>
+        <v>14.72805419104705</v>
       </c>
       <c r="G59">
         <v>2.19</v>
@@ -6113,37 +6113,37 @@
         <v>1.772</v>
       </c>
       <c r="M59">
-        <v>2.124801142224229</v>
+        <v>2.162078355245706</v>
       </c>
       <c r="N59">
-        <v>-0.3528011422242294</v>
+        <v>-0.3900783552457068</v>
       </c>
       <c r="O59">
-        <v>-0.05150896676473749</v>
+        <v>-0.05695143986587319</v>
       </c>
       <c r="P59">
-        <v>-0.3012921754594919</v>
+        <v>-0.3331269153798336</v>
       </c>
       <c r="Q59">
-        <v>0.3417078245405081</v>
+        <v>0.3098730846201664</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1726960578105828</v>
+        <v>0.1757173925203586</v>
       </c>
       <c r="T59">
-        <v>2.930624891699373</v>
+        <v>3.000401674835073</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.1217582176792233</v>
+        <v>0.1196589380640643</v>
       </c>
       <c r="W59">
-        <v>0.12892589364469</v>
+        <v>0.1292340678921954</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8339603950631731</v>
+        <v>0.8195817675620841</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1487570642360239</v>
+        <v>0.1497670642360239</v>
       </c>
       <c r="C60">
-        <v>2.010260442566892</v>
+        <v>1.636640978360205</v>
       </c>
       <c r="D60">
-        <v>14.54831463361393</v>
+        <v>14.4286271382184</v>
       </c>
       <c r="E60">
-        <v>10.83485730993145</v>
+        <v>11.08878927874261</v>
       </c>
       <c r="F60">
-        <v>14.72805419104704</v>
+        <v>14.9819861598582</v>
       </c>
       <c r="G60">
         <v>2.19</v>
@@ -6195,37 +6195,37 @@
         <v>1.772</v>
       </c>
       <c r="M60">
-        <v>2.162078355245706</v>
+        <v>2.199355568267184</v>
       </c>
       <c r="N60">
-        <v>-0.3900783552457068</v>
+        <v>-0.4273555682671841</v>
       </c>
       <c r="O60">
-        <v>-0.05695143986587319</v>
+        <v>-0.06239391296700888</v>
       </c>
       <c r="P60">
-        <v>-0.3331269153798336</v>
+        <v>-0.3649616553001753</v>
       </c>
       <c r="Q60">
-        <v>0.3098730846201664</v>
+        <v>0.2780383446998247</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1757173925203586</v>
+        <v>0.178886109411099</v>
       </c>
       <c r="T60">
-        <v>3.000401674835071</v>
+        <v>3.073582203489585</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1196589380640643</v>
+        <v>0.1176308204697581</v>
       </c>
       <c r="W60">
-        <v>0.1292340678921954</v>
+        <v>0.1295317955550395</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8195817675620841</v>
+        <v>0.8056905511627268</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1497670642360239</v>
+        <v>0.1842714180258495</v>
       </c>
       <c r="C61">
-        <v>1.636640978360205</v>
+        <v>-1.782821072541603</v>
       </c>
       <c r="D61">
-        <v>14.4286271382184</v>
+        <v>11.26309705612775</v>
       </c>
       <c r="E61">
-        <v>11.08878927874261</v>
+        <v>11.34272124755376</v>
       </c>
       <c r="F61">
-        <v>14.9819861598582</v>
+        <v>15.23591812866935</v>
       </c>
       <c r="G61">
         <v>2.19</v>
@@ -6277,45 +6277,45 @@
         <v>1.772</v>
       </c>
       <c r="M61">
-        <v>2.199355568267184</v>
+        <v>3.059372360236806</v>
       </c>
       <c r="N61">
-        <v>-0.4273555682671841</v>
+        <v>-1.287372360236807</v>
       </c>
       <c r="O61">
-        <v>-0.06239391296700888</v>
+        <v>-0.1879563645945738</v>
       </c>
       <c r="P61">
-        <v>-0.3649616553001753</v>
+        <v>-1.099415995642233</v>
       </c>
       <c r="Q61">
-        <v>0.2780383446998247</v>
+        <v>-0.4564159956422331</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.178886109411099</v>
+        <v>0.1849491466209405</v>
       </c>
       <c r="T61">
-        <v>3.073582203489585</v>
+        <v>3.213606157527495</v>
       </c>
       <c r="U61">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1176308204697581</v>
+        <v>0.08456375018697453</v>
       </c>
       <c r="W61">
-        <v>0.1295317955550395</v>
+        <v>0.1838195989624555</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.8056905511627268</v>
+        <v>0.5792037684039351</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1842714180258495</v>
+        <v>0.1858214180258495</v>
       </c>
       <c r="C62">
-        <v>-1.782821072541603</v>
+        <v>-2.146673319878918</v>
       </c>
       <c r="D62">
-        <v>11.26309705612775</v>
+        <v>11.15317677760159</v>
       </c>
       <c r="E62">
-        <v>11.34272124755376</v>
+        <v>11.59665321636492</v>
       </c>
       <c r="F62">
-        <v>15.23591812866935</v>
+        <v>15.48985009748051</v>
       </c>
       <c r="G62">
         <v>2.19</v>
@@ -6359,37 +6359,37 @@
         <v>1.772</v>
       </c>
       <c r="M62">
-        <v>3.059372360236806</v>
+        <v>3.110361899574087</v>
       </c>
       <c r="N62">
-        <v>-1.287372360236807</v>
+        <v>-1.338361899574087</v>
       </c>
       <c r="O62">
-        <v>-0.1879563645945738</v>
+        <v>-0.1954008373378167</v>
       </c>
       <c r="P62">
-        <v>-1.099415995642233</v>
+        <v>-1.142961062236271</v>
       </c>
       <c r="Q62">
-        <v>-0.4564159956422331</v>
+        <v>-0.4999610622362707</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1849491466209405</v>
+        <v>0.1885170734573749</v>
       </c>
       <c r="T62">
-        <v>3.213606157527495</v>
+        <v>3.296006315412816</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.08456375018697453</v>
+        <v>0.0831774592003028</v>
       </c>
       <c r="W62">
-        <v>0.1838195989624555</v>
+        <v>0.1840979661925792</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5792037684039351</v>
+        <v>0.5697086246596083</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1858214180258495</v>
+        <v>0.1873714180258495</v>
       </c>
       <c r="C63">
-        <v>-2.146673319878918</v>
+        <v>-2.508400806956795</v>
       </c>
       <c r="D63">
-        <v>11.15317677760159</v>
+        <v>11.04538125933487</v>
       </c>
       <c r="E63">
-        <v>11.59665321636492</v>
+        <v>11.85058518517607</v>
       </c>
       <c r="F63">
-        <v>15.48985009748051</v>
+        <v>15.74378206629167</v>
       </c>
       <c r="G63">
         <v>2.19</v>
@@ -6441,37 +6441,37 @@
         <v>1.772</v>
       </c>
       <c r="M63">
-        <v>3.110361899574087</v>
+        <v>3.161351438911367</v>
       </c>
       <c r="N63">
-        <v>-1.338361899574087</v>
+        <v>-1.389351438911367</v>
       </c>
       <c r="O63">
-        <v>-0.1954008373378167</v>
+        <v>-0.2028453100810596</v>
       </c>
       <c r="P63">
-        <v>-1.142961062236271</v>
+        <v>-1.186506128830307</v>
       </c>
       <c r="Q63">
-        <v>-0.4999610622362707</v>
+        <v>-0.5435061288303074</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1885170734573749</v>
+        <v>0.1922727859167795</v>
       </c>
       <c r="T63">
-        <v>3.296006315412816</v>
+        <v>3.382743323713152</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.0831774592003028</v>
+        <v>0.08183588727771729</v>
       </c>
       <c r="W63">
-        <v>0.1840979661925792</v>
+        <v>0.1843673538346344</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5697086246596083</v>
+        <v>0.560519775874776</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1873714180258495</v>
+        <v>0.1889214180258496</v>
       </c>
       <c r="C64">
-        <v>-2.508400806956795</v>
+        <v>-2.868064551499289</v>
       </c>
       <c r="D64">
-        <v>11.04538125933487</v>
+        <v>10.93964948360354</v>
       </c>
       <c r="E64">
-        <v>11.85058518517607</v>
+        <v>12.10451715398723</v>
       </c>
       <c r="F64">
-        <v>15.74378206629167</v>
+        <v>15.99771403510282</v>
       </c>
       <c r="G64">
         <v>2.19</v>
@@ -6523,37 +6523,37 @@
         <v>1.772</v>
       </c>
       <c r="M64">
-        <v>3.161351438911367</v>
+        <v>3.212340978248647</v>
       </c>
       <c r="N64">
-        <v>-1.389351438911367</v>
+        <v>-1.440340978248648</v>
       </c>
       <c r="O64">
-        <v>-0.2028453100810596</v>
+        <v>-0.2102897828243025</v>
       </c>
       <c r="P64">
-        <v>-1.186506128830307</v>
+        <v>-1.230051195424345</v>
       </c>
       <c r="Q64">
-        <v>-0.5435061288303074</v>
+        <v>-0.5870511954243451</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1922727859167795</v>
+        <v>0.1962315098604762</v>
       </c>
       <c r="T64">
-        <v>3.382743323713152</v>
+        <v>3.474168818948643</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.08183588727771729</v>
+        <v>0.08053690493997571</v>
       </c>
       <c r="W64">
-        <v>0.1843673538346344</v>
+        <v>0.1846281894880529</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.560519775874776</v>
+        <v>0.5516226365751762</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1889214180258496</v>
+        <v>0.1904714180258495</v>
       </c>
       <c r="C65">
-        <v>-2.868064551499289</v>
+        <v>-3.225723257017577</v>
       </c>
       <c r="D65">
-        <v>10.93964948360354</v>
+        <v>10.8359227468964</v>
       </c>
       <c r="E65">
-        <v>12.10451715398723</v>
+        <v>12.35844912279839</v>
       </c>
       <c r="F65">
-        <v>15.99771403510282</v>
+        <v>16.25164600391398</v>
       </c>
       <c r="G65">
         <v>2.19</v>
@@ -6605,37 +6605,37 @@
         <v>1.772</v>
       </c>
       <c r="M65">
-        <v>3.212340978248647</v>
+        <v>3.263330517585927</v>
       </c>
       <c r="N65">
-        <v>-1.440340978248648</v>
+        <v>-1.491330517585928</v>
       </c>
       <c r="O65">
-        <v>-0.2102897828243025</v>
+        <v>-0.2177342555675454</v>
       </c>
       <c r="P65">
-        <v>-1.230051195424345</v>
+        <v>-1.273596262018382</v>
       </c>
       <c r="Q65">
-        <v>-0.5870511954243451</v>
+        <v>-0.6305962620183823</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1962315098604762</v>
+        <v>0.2004101629121561</v>
       </c>
       <c r="T65">
-        <v>3.474168818948643</v>
+        <v>3.570673508363883</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.08053690493997571</v>
+        <v>0.07927851580028861</v>
       </c>
       <c r="W65">
-        <v>0.1846281894880529</v>
+        <v>0.1848808740273021</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5516226365751762</v>
+        <v>0.5430035328786891</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1904714180258495</v>
+        <v>0.1920214180258495</v>
       </c>
       <c r="C66">
-        <v>-3.225723257017577</v>
+        <v>-3.581433421493113</v>
       </c>
       <c r="D66">
-        <v>10.8359227468964</v>
+        <v>10.73414455123202</v>
       </c>
       <c r="E66">
-        <v>12.35844912279839</v>
+        <v>12.61238109160954</v>
       </c>
       <c r="F66">
-        <v>16.25164600391398</v>
+        <v>16.50557797272513</v>
       </c>
       <c r="G66">
         <v>2.19</v>
@@ -6687,37 +6687,37 @@
         <v>1.772</v>
       </c>
       <c r="M66">
-        <v>3.263330517585927</v>
+        <v>3.314320056923207</v>
       </c>
       <c r="N66">
-        <v>-1.491330517585928</v>
+        <v>-1.542320056923207</v>
       </c>
       <c r="O66">
-        <v>-0.2177342555675454</v>
+        <v>-0.2251787283107883</v>
       </c>
       <c r="P66">
-        <v>-1.273596262018382</v>
+        <v>-1.317141328612419</v>
       </c>
       <c r="Q66">
-        <v>-0.6305962620183823</v>
+        <v>-0.6741413286124192</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2004101629121561</v>
+        <v>0.2048275961382177</v>
       </c>
       <c r="T66">
-        <v>3.570673508363883</v>
+        <v>3.672692751459994</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.07927851580028861</v>
+        <v>0.07805884632643803</v>
       </c>
       <c r="W66">
-        <v>0.1848808740273021</v>
+        <v>0.1851257836576513</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5430035328786891</v>
+        <v>0.5346496323728631</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1920214180258495</v>
+        <v>0.1935714180258495</v>
       </c>
       <c r="C67">
-        <v>-3.581433421493113</v>
+        <v>-3.9352494399928</v>
       </c>
       <c r="D67">
-        <v>10.73414455123202</v>
+        <v>10.63426050154349</v>
       </c>
       <c r="E67">
-        <v>12.61238109160954</v>
+        <v>12.8663130604207</v>
       </c>
       <c r="F67">
-        <v>16.50557797272513</v>
+        <v>16.75950994153629</v>
       </c>
       <c r="G67">
         <v>2.19</v>
@@ -6769,37 +6769,37 @@
         <v>1.772</v>
       </c>
       <c r="M67">
-        <v>3.314320056923207</v>
+        <v>3.365309596260487</v>
       </c>
       <c r="N67">
-        <v>-1.542320056923207</v>
+        <v>-1.593309596260488</v>
       </c>
       <c r="O67">
-        <v>-0.2251787283107883</v>
+        <v>-0.2326232010540312</v>
       </c>
       <c r="P67">
-        <v>-1.317141328612419</v>
+        <v>-1.360686395206456</v>
       </c>
       <c r="Q67">
-        <v>-0.6741413286124192</v>
+        <v>-0.7176863952064563</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2048275961382177</v>
+        <v>0.209504878377577</v>
       </c>
       <c r="T67">
-        <v>3.672692751459994</v>
+        <v>3.780713126502935</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.07805884632643803</v>
+        <v>0.07687613653361319</v>
       </c>
       <c r="W67">
-        <v>0.1851257836576513</v>
+        <v>0.1853632717840505</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5346496323728631</v>
+        <v>0.5265488803672138</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1935714180258495</v>
+        <v>0.1951214180258495</v>
       </c>
       <c r="C68">
-        <v>-3.9352494399928</v>
+        <v>-4.287223701607831</v>
       </c>
       <c r="D68">
-        <v>10.63426050154349</v>
+        <v>10.53621820873962</v>
       </c>
       <c r="E68">
-        <v>12.8663130604207</v>
+        <v>13.12024502923186</v>
       </c>
       <c r="F68">
-        <v>16.75950994153629</v>
+        <v>17.01344191034745</v>
       </c>
       <c r="G68">
         <v>2.19</v>
@@ -6851,37 +6851,37 @@
         <v>1.772</v>
       </c>
       <c r="M68">
-        <v>3.365309596260487</v>
+        <v>3.416299135597768</v>
       </c>
       <c r="N68">
-        <v>-1.593309596260488</v>
+        <v>-1.644299135597769</v>
       </c>
       <c r="O68">
-        <v>-0.2326232010540312</v>
+        <v>-0.2400676737972742</v>
       </c>
       <c r="P68">
-        <v>-1.360686395206456</v>
+        <v>-1.404231461800494</v>
       </c>
       <c r="Q68">
-        <v>-0.7176863952064563</v>
+        <v>-0.7612314618004943</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.209504878377577</v>
+        <v>0.2144656322678067</v>
       </c>
       <c r="T68">
-        <v>3.780713126502935</v>
+        <v>3.895280190942418</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.07687613653361319</v>
+        <v>0.07572873151072343</v>
       </c>
       <c r="W68">
-        <v>0.1853632717840505</v>
+        <v>0.1855936707126467</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5265488803672138</v>
+        <v>0.5186899418542701</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1951214180258495</v>
+        <v>0.1966714180258495</v>
       </c>
       <c r="C69">
-        <v>-4.287223701607831</v>
+        <v>-4.637406681079144</v>
       </c>
       <c r="D69">
-        <v>10.53621820873962</v>
+        <v>10.43996719807946</v>
       </c>
       <c r="E69">
-        <v>13.12024502923186</v>
+        <v>13.37417699804301</v>
       </c>
       <c r="F69">
-        <v>17.01344191034745</v>
+        <v>17.2673738791586</v>
       </c>
       <c r="G69">
         <v>2.19</v>
@@ -6933,37 +6933,37 @@
         <v>1.772</v>
       </c>
       <c r="M69">
-        <v>3.416299135597768</v>
+        <v>3.467288674935048</v>
       </c>
       <c r="N69">
-        <v>-1.644299135597769</v>
+        <v>-1.695288674935048</v>
       </c>
       <c r="O69">
-        <v>-0.2400676737972742</v>
+        <v>-0.247512146540517</v>
       </c>
       <c r="P69">
-        <v>-1.404231461800494</v>
+        <v>-1.447776528394531</v>
       </c>
       <c r="Q69">
-        <v>-0.7612314618004943</v>
+        <v>-0.8047765283945312</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2144656322678067</v>
+        <v>0.2197364332761756</v>
       </c>
       <c r="T69">
-        <v>3.895280190942418</v>
+        <v>4.01700769690937</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.07572873151072343</v>
+        <v>0.07461507369438927</v>
       </c>
       <c r="W69">
-        <v>0.1855936707126467</v>
+        <v>0.1858172932021666</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5186899418542701</v>
+        <v>0.5110621485917074</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1966714180258495</v>
+        <v>0.1982214180258495</v>
       </c>
       <c r="C70">
-        <v>-4.637406681079144</v>
+        <v>-4.985847025446239</v>
       </c>
       <c r="D70">
-        <v>10.43996719807946</v>
+        <v>10.34545882252352</v>
       </c>
       <c r="E70">
-        <v>13.37417699804301</v>
+        <v>13.62810896685417</v>
       </c>
       <c r="F70">
-        <v>17.2673738791586</v>
+        <v>17.52130584796976</v>
       </c>
       <c r="G70">
         <v>2.19</v>
@@ -7015,37 +7015,37 @@
         <v>1.772</v>
       </c>
       <c r="M70">
-        <v>3.467288674935048</v>
+        <v>3.518278214272328</v>
       </c>
       <c r="N70">
-        <v>-1.695288674935048</v>
+        <v>-1.746278214272328</v>
       </c>
       <c r="O70">
-        <v>-0.247512146540517</v>
+        <v>-0.2549566192837599</v>
       </c>
       <c r="P70">
-        <v>-1.447776528394531</v>
+        <v>-1.491321594988568</v>
       </c>
       <c r="Q70">
-        <v>-0.8047765283945312</v>
+        <v>-0.8483215949885683</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2197364332761756</v>
+        <v>0.2253472859625039</v>
       </c>
       <c r="T70">
-        <v>4.01700769690937</v>
+        <v>4.146588590358059</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.07461507369438927</v>
+        <v>0.07353369581476045</v>
       </c>
       <c r="W70">
-        <v>0.1858172932021666</v>
+        <v>0.1860344338803961</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5110621485917074</v>
+        <v>0.5036554507860305</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1982214180258495</v>
+        <v>0.224713002998372</v>
       </c>
       <c r="C71">
-        <v>-4.985847025446239</v>
+        <v>-6.625961296065869</v>
       </c>
       <c r="D71">
-        <v>10.34545882252352</v>
+        <v>8.959276520715047</v>
       </c>
       <c r="E71">
-        <v>13.62810896685417</v>
+        <v>13.88204093566532</v>
       </c>
       <c r="F71">
-        <v>17.52130584796976</v>
+        <v>17.77523781678092</v>
       </c>
       <c r="G71">
         <v>2.19</v>
@@ -7097,45 +7097,45 @@
         <v>1.772</v>
       </c>
       <c r="M71">
-        <v>3.518278214272328</v>
+        <v>4.19140107719694</v>
       </c>
       <c r="N71">
-        <v>-1.746278214272328</v>
+        <v>-2.419401077196941</v>
       </c>
       <c r="O71">
-        <v>-0.2549566192837599</v>
+        <v>-0.3532325572707534</v>
       </c>
       <c r="P71">
-        <v>-1.491321594988568</v>
+        <v>-2.066168519926188</v>
       </c>
       <c r="Q71">
-        <v>-0.8483215949885683</v>
+        <v>-1.423168519926188</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2253472859625039</v>
+        <v>0.2328041454029958</v>
       </c>
       <c r="T71">
-        <v>4.146588590358059</v>
+        <v>4.318802434249326</v>
       </c>
       <c r="U71">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.07353369581476045</v>
+        <v>0.06172446760285162</v>
       </c>
       <c r="W71">
-        <v>0.1860344338803961</v>
+        <v>0.2212453705392476</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.5036554507860305</v>
+        <v>0.4227703260469289</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.224713002998372</v>
+        <v>0.2266130029983721</v>
       </c>
       <c r="C72">
-        <v>-6.625961296065869</v>
+        <v>-6.965170992030822</v>
       </c>
       <c r="D72">
-        <v>8.959276520715047</v>
+        <v>8.873998793561249</v>
       </c>
       <c r="E72">
-        <v>13.88204093566532</v>
+        <v>14.13597290447648</v>
       </c>
       <c r="F72">
-        <v>17.77523781678092</v>
+        <v>18.02916978559207</v>
       </c>
       <c r="G72">
         <v>2.19</v>
@@ -7179,37 +7179,37 @@
         <v>1.772</v>
       </c>
       <c r="M72">
-        <v>4.19140107719694</v>
+        <v>4.25127823544261</v>
       </c>
       <c r="N72">
-        <v>-2.419401077196941</v>
+        <v>-2.479278235442611</v>
       </c>
       <c r="O72">
-        <v>-0.3532325572707534</v>
+        <v>-0.3619746223746212</v>
       </c>
       <c r="P72">
-        <v>-2.066168519926188</v>
+        <v>-2.11730361306799</v>
       </c>
       <c r="Q72">
-        <v>-1.423168519926188</v>
+        <v>-1.47430361306799</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2328041454029958</v>
+        <v>0.2392525642099957</v>
       </c>
       <c r="T72">
-        <v>4.318802434249326</v>
+        <v>4.467726656119994</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.06172446760285162</v>
+        <v>0.06085510890421991</v>
       </c>
       <c r="W72">
-        <v>0.2212453705392476</v>
+        <v>0.221450365320385</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4227703260469289</v>
+        <v>0.4168158144124652</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.226613002998372</v>
+        <v>0.228513002998372</v>
       </c>
       <c r="C73">
-        <v>-6.965170992030822</v>
+        <v>-7.302772584257497</v>
       </c>
       <c r="D73">
-        <v>8.873998793561249</v>
+        <v>8.79032917014573</v>
       </c>
       <c r="E73">
-        <v>14.13597290447648</v>
+        <v>14.38990487328763</v>
       </c>
       <c r="F73">
-        <v>18.02916978559207</v>
+        <v>18.28310175440323</v>
       </c>
       <c r="G73">
         <v>2.19</v>
@@ -7261,37 +7261,37 @@
         <v>1.772</v>
       </c>
       <c r="M73">
-        <v>4.25127823544261</v>
+        <v>4.311155393688281</v>
       </c>
       <c r="N73">
-        <v>-2.479278235442611</v>
+        <v>-2.539155393688282</v>
       </c>
       <c r="O73">
-        <v>-0.3619746223746212</v>
+        <v>-0.3707166874784891</v>
       </c>
       <c r="P73">
-        <v>-2.11730361306799</v>
+        <v>-2.168438706209793</v>
       </c>
       <c r="Q73">
-        <v>-1.47430361306799</v>
+        <v>-1.525438706209793</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2392525642099956</v>
+        <v>0.2461615843603526</v>
       </c>
       <c r="T73">
-        <v>4.467726656119992</v>
+        <v>4.627288322409992</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.06085510890421991</v>
+        <v>0.06000989905832797</v>
       </c>
       <c r="W73">
-        <v>0.221450365320385</v>
+        <v>0.2216496658020463</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4168158144124652</v>
+        <v>0.4110267058789586</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.228513002998372</v>
+        <v>0.230413002998372</v>
       </c>
       <c r="C74">
-        <v>-7.302772584257497</v>
+        <v>-7.638811134505699</v>
       </c>
       <c r="D74">
-        <v>8.79032917014573</v>
+        <v>8.708222588708683</v>
       </c>
       <c r="E74">
-        <v>14.38990487328763</v>
+        <v>14.64383684209879</v>
       </c>
       <c r="F74">
-        <v>18.28310175440323</v>
+        <v>18.53703372321438</v>
       </c>
       <c r="G74">
         <v>2.19</v>
@@ -7343,37 +7343,37 @@
         <v>1.772</v>
       </c>
       <c r="M74">
-        <v>4.311155393688281</v>
+        <v>4.371032551933951</v>
       </c>
       <c r="N74">
-        <v>-2.539155393688282</v>
+        <v>-2.599032551933952</v>
       </c>
       <c r="O74">
-        <v>-0.3707166874784891</v>
+        <v>-0.379458752582357</v>
       </c>
       <c r="P74">
-        <v>-2.168438706209793</v>
+        <v>-2.219573799351595</v>
       </c>
       <c r="Q74">
-        <v>-1.525438706209793</v>
+        <v>-1.576573799351595</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2461615843603526</v>
+        <v>0.2535823837811064</v>
       </c>
       <c r="T74">
-        <v>4.627288322409992</v>
+        <v>4.798669371388139</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.06000989905832797</v>
+        <v>0.05918784564657005</v>
       </c>
       <c r="W74">
-        <v>0.2216496658020463</v>
+        <v>0.2218435059965388</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4110267058789586</v>
+        <v>0.4053962030586989</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.230413002998372</v>
+        <v>0.232313002998372</v>
       </c>
       <c r="C75">
-        <v>-7.638811134505699</v>
+        <v>-7.973330036507575</v>
       </c>
       <c r="D75">
-        <v>8.708222588708683</v>
+        <v>8.627635655517963</v>
       </c>
       <c r="E75">
-        <v>14.64383684209879</v>
+        <v>14.89776881090994</v>
       </c>
       <c r="F75">
-        <v>18.53703372321438</v>
+        <v>18.79096569202554</v>
       </c>
       <c r="G75">
         <v>2.19</v>
@@ -7425,37 +7425,37 @@
         <v>1.772</v>
       </c>
       <c r="M75">
-        <v>4.371032551933951</v>
+        <v>4.430909710179622</v>
       </c>
       <c r="N75">
-        <v>-2.599032551933952</v>
+        <v>-2.658909710179622</v>
       </c>
       <c r="O75">
-        <v>-0.379458752582357</v>
+        <v>-0.3882008176862248</v>
       </c>
       <c r="P75">
-        <v>-2.219573799351595</v>
+        <v>-2.270708892493397</v>
       </c>
       <c r="Q75">
-        <v>-1.576573799351595</v>
+        <v>-1.627708892493397</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2535823837811064</v>
+        <v>0.2615740139265335</v>
       </c>
       <c r="T75">
-        <v>4.798669371388139</v>
+        <v>4.983233577979991</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.05918784564657005</v>
+        <v>0.05838800989458939</v>
       </c>
       <c r="W75">
-        <v>0.2218435059965388</v>
+        <v>0.2220321072668558</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4053962030586989</v>
+        <v>0.3999178759903382</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.232313002998372</v>
+        <v>0.234213002998372</v>
       </c>
       <c r="C76">
-        <v>-7.973330036507575</v>
+        <v>-8.306371092440559</v>
       </c>
       <c r="D76">
-        <v>8.627635655517963</v>
+        <v>8.548526568396138</v>
       </c>
       <c r="E76">
-        <v>14.89776881090994</v>
+        <v>15.1517007797211</v>
       </c>
       <c r="F76">
-        <v>18.79096569202554</v>
+        <v>19.0448976608367</v>
       </c>
       <c r="G76">
         <v>2.19</v>
@@ -7507,37 +7507,37 @@
         <v>1.772</v>
       </c>
       <c r="M76">
-        <v>4.430909710179622</v>
+        <v>4.490786868425293</v>
       </c>
       <c r="N76">
-        <v>-2.658909710179622</v>
+        <v>-2.718786868425294</v>
       </c>
       <c r="O76">
-        <v>-0.3882008176862248</v>
+        <v>-0.3969428827900929</v>
       </c>
       <c r="P76">
-        <v>-2.270708892493397</v>
+        <v>-2.321843985635201</v>
       </c>
       <c r="Q76">
-        <v>-1.627708892493397</v>
+        <v>-1.678843985635201</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2615740139265335</v>
+        <v>0.2702049744835949</v>
       </c>
       <c r="T76">
-        <v>4.983233577979991</v>
+        <v>5.182562921099191</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05838800989458939</v>
+        <v>0.05760950309599484</v>
       </c>
       <c r="W76">
-        <v>0.2220321072668558</v>
+        <v>0.2222156791699644</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3999178759903382</v>
+        <v>0.3945856376438003</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.234213002998372</v>
+        <v>0.2361130029983721</v>
       </c>
       <c r="C77">
-        <v>-8.306371092440559</v>
+        <v>-8.637974585231353</v>
       </c>
       <c r="D77">
-        <v>8.548526568396138</v>
+        <v>8.470855044416499</v>
       </c>
       <c r="E77">
-        <v>15.1517007797211</v>
+        <v>15.40563274853226</v>
       </c>
       <c r="F77">
-        <v>19.0448976608367</v>
+        <v>19.29882962964785</v>
       </c>
       <c r="G77">
         <v>2.19</v>
@@ -7589,37 +7589,37 @@
         <v>1.772</v>
       </c>
       <c r="M77">
-        <v>4.490786868425293</v>
+        <v>4.550664026670963</v>
       </c>
       <c r="N77">
-        <v>-2.718786868425294</v>
+        <v>-2.778664026670964</v>
       </c>
       <c r="O77">
-        <v>-0.3969428827900929</v>
+        <v>-0.4056849478939608</v>
       </c>
       <c r="P77">
-        <v>-2.321843985635201</v>
+        <v>-2.372979078777004</v>
       </c>
       <c r="Q77">
-        <v>-1.678843985635201</v>
+        <v>-1.729979078777004</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2702049744835949</v>
+        <v>0.2795551817537447</v>
       </c>
       <c r="T77">
-        <v>5.182562921099191</v>
+        <v>5.398503042811658</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.05760950309599484</v>
+        <v>0.05685148331841597</v>
       </c>
       <c r="W77">
-        <v>0.2222156791699644</v>
+        <v>0.2223944202335175</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3945856376438003</v>
+        <v>0.3893937213590135</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2361130029983721</v>
+        <v>0.2380130029983721</v>
       </c>
       <c r="C78">
-        <v>-8.637974585231353</v>
+        <v>-8.968179346953663</v>
       </c>
       <c r="D78">
-        <v>8.470855044416499</v>
+        <v>8.394582251505344</v>
       </c>
       <c r="E78">
-        <v>15.40563274853226</v>
+        <v>15.65956471734341</v>
       </c>
       <c r="F78">
-        <v>19.29882962964785</v>
+        <v>19.55276159845901</v>
       </c>
       <c r="G78">
         <v>2.19</v>
@@ -7671,37 +7671,37 @@
         <v>1.772</v>
       </c>
       <c r="M78">
-        <v>4.550664026670963</v>
+        <v>4.610541184916634</v>
       </c>
       <c r="N78">
-        <v>-2.778664026670964</v>
+        <v>-2.838541184916635</v>
       </c>
       <c r="O78">
-        <v>-0.4056849478939608</v>
+        <v>-0.4144270129978287</v>
       </c>
       <c r="P78">
-        <v>-2.372979078777004</v>
+        <v>-2.424114171918807</v>
       </c>
       <c r="Q78">
-        <v>-1.729979078777004</v>
+        <v>-1.781114171918807</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2795551817537447</v>
+        <v>0.2897184505256467</v>
       </c>
       <c r="T78">
-        <v>5.398503042811658</v>
+        <v>5.633220566412165</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.05685148331841597</v>
+        <v>0.05611315236622874</v>
       </c>
       <c r="W78">
-        <v>0.2223944202335175</v>
+        <v>0.2225685186720433</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3893937213590135</v>
+        <v>0.3843366600426626</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2380130029983721</v>
+        <v>0.239913002998372</v>
       </c>
       <c r="C79">
-        <v>-8.968179346953663</v>
+        <v>-9.297022823563788</v>
       </c>
       <c r="D79">
-        <v>8.394582251505344</v>
+        <v>8.319670743706375</v>
       </c>
       <c r="E79">
-        <v>15.65956471734341</v>
+        <v>15.91349668615457</v>
       </c>
       <c r="F79">
-        <v>19.55276159845901</v>
+        <v>19.80669356727016</v>
       </c>
       <c r="G79">
         <v>2.19</v>
@@ -7753,37 +7753,37 @@
         <v>1.772</v>
       </c>
       <c r="M79">
-        <v>4.610541184916634</v>
+        <v>4.670418343162305</v>
       </c>
       <c r="N79">
-        <v>-2.838541184916635</v>
+        <v>-2.898418343162305</v>
       </c>
       <c r="O79">
-        <v>-0.4144270129978287</v>
+        <v>-0.4231690781016965</v>
       </c>
       <c r="P79">
-        <v>-2.424114171918807</v>
+        <v>-2.475249265060609</v>
       </c>
       <c r="Q79">
-        <v>-1.781114171918807</v>
+        <v>-1.832249265060609</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2897184505256467</v>
+        <v>0.300805652822267</v>
       </c>
       <c r="T79">
-        <v>5.633220566412165</v>
+        <v>5.889276046703626</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.05611315236622874</v>
+        <v>0.05539375297691813</v>
       </c>
       <c r="W79">
-        <v>0.2225685186720433</v>
+        <v>0.2227381530480427</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3843366600426626</v>
+        <v>0.3794092669651926</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.239913002998372</v>
+        <v>0.2418130029983721</v>
       </c>
       <c r="C80">
-        <v>-9.297022823563788</v>
+        <v>-9.624541136200669</v>
       </c>
       <c r="D80">
-        <v>8.319670743706375</v>
+        <v>8.246084399880649</v>
       </c>
       <c r="E80">
-        <v>15.91349668615457</v>
+        <v>16.16742865496573</v>
       </c>
       <c r="F80">
-        <v>19.80669356727016</v>
+        <v>20.06062553608132</v>
       </c>
       <c r="G80">
         <v>2.19</v>
@@ -7835,37 +7835,37 @@
         <v>1.772</v>
       </c>
       <c r="M80">
-        <v>4.670418343162305</v>
+        <v>4.730295501407975</v>
       </c>
       <c r="N80">
-        <v>-2.898418343162305</v>
+        <v>-2.958295501407975</v>
       </c>
       <c r="O80">
-        <v>-0.4231690781016965</v>
+        <v>-0.4319111432055643</v>
       </c>
       <c r="P80">
-        <v>-2.475249265060609</v>
+        <v>-2.526384358202411</v>
       </c>
       <c r="Q80">
-        <v>-1.832249265060609</v>
+        <v>-1.883384358202411</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.300805652822267</v>
+        <v>0.3129487791471368</v>
       </c>
       <c r="T80">
-        <v>5.889276046703626</v>
+        <v>6.169717763213323</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05539375297691813</v>
+        <v>0.05469256623037486</v>
       </c>
       <c r="W80">
-        <v>0.2227381530480427</v>
+        <v>0.2229034928828776</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3794092669651926</v>
+        <v>0.3746066180162662</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2418130029983721</v>
+        <v>0.2437130029983721</v>
       </c>
       <c r="C81">
-        <v>-9.624541136200669</v>
+        <v>-9.950769139261389</v>
       </c>
       <c r="D81">
-        <v>8.246084399880649</v>
+        <v>8.173788365631088</v>
       </c>
       <c r="E81">
-        <v>16.16742865496573</v>
+        <v>16.42136062377688</v>
       </c>
       <c r="F81">
-        <v>20.06062553608132</v>
+        <v>20.31455750489248</v>
       </c>
       <c r="G81">
         <v>2.19</v>
@@ -7917,37 +7917,37 @@
         <v>1.772</v>
       </c>
       <c r="M81">
-        <v>4.730295501407975</v>
+        <v>4.790172659653646</v>
       </c>
       <c r="N81">
-        <v>-2.958295501407975</v>
+        <v>-3.018172659653647</v>
       </c>
       <c r="O81">
-        <v>-0.4319111432055643</v>
+        <v>-0.4406532083094324</v>
       </c>
       <c r="P81">
-        <v>-2.526384358202411</v>
+        <v>-2.577519451344215</v>
       </c>
       <c r="Q81">
-        <v>-1.883384358202411</v>
+        <v>-1.934519451344215</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3129487791471368</v>
+        <v>0.3263062181044937</v>
       </c>
       <c r="T81">
-        <v>6.169717763213323</v>
+        <v>6.478203651373991</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05469256623037486</v>
+        <v>0.05400890915249516</v>
       </c>
       <c r="W81">
-        <v>0.2229034928828776</v>
+        <v>0.2230646992218417</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3746066180162662</v>
+        <v>0.3699240352910628</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2437130029983721</v>
+        <v>0.245613002998372</v>
       </c>
       <c r="C82">
-        <v>-9.950769139261389</v>
+        <v>-10.27574047544816</v>
       </c>
       <c r="D82">
-        <v>8.173788365631088</v>
+        <v>8.102748998255477</v>
       </c>
       <c r="E82">
-        <v>16.42136062377688</v>
+        <v>16.67529259258804</v>
       </c>
       <c r="F82">
-        <v>20.31455750489248</v>
+        <v>20.56848947370363</v>
       </c>
       <c r="G82">
         <v>2.19</v>
@@ -7999,37 +7999,37 @@
         <v>1.772</v>
       </c>
       <c r="M82">
-        <v>4.790172659653646</v>
+        <v>4.850049817899317</v>
       </c>
       <c r="N82">
-        <v>-3.018172659653647</v>
+        <v>-3.078049817899317</v>
       </c>
       <c r="O82">
-        <v>-0.4406532083094324</v>
+        <v>-0.4493952734133003</v>
       </c>
       <c r="P82">
-        <v>-2.577519451344215</v>
+        <v>-2.628654544486017</v>
       </c>
       <c r="Q82">
-        <v>-1.934519451344215</v>
+        <v>-1.985654544486017</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3263062181044937</v>
+        <v>0.3410697032678881</v>
       </c>
       <c r="T82">
-        <v>6.478203651373991</v>
+        <v>6.819161738288411</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05400890915249516</v>
+        <v>0.05334213249629153</v>
       </c>
       <c r="W82">
-        <v>0.2230646992218417</v>
+        <v>0.2232219251573745</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3699240352910628</v>
+        <v>0.3653570718924076</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.245613002998372</v>
+        <v>0.2475130029983721</v>
       </c>
       <c r="C83">
-        <v>-10.27574047544816</v>
+        <v>-10.5994876279696</v>
       </c>
       <c r="D83">
-        <v>8.102748998255477</v>
+        <v>8.032933814545192</v>
       </c>
       <c r="E83">
-        <v>16.67529259258804</v>
+        <v>16.9292245613992</v>
       </c>
       <c r="F83">
-        <v>20.56848947370363</v>
+        <v>20.82242144251479</v>
       </c>
       <c r="G83">
         <v>2.19</v>
@@ -8081,37 +8081,37 @@
         <v>1.772</v>
       </c>
       <c r="M83">
-        <v>4.850049817899317</v>
+        <v>4.909926976144988</v>
       </c>
       <c r="N83">
-        <v>-3.078049817899317</v>
+        <v>-3.137926976144988</v>
       </c>
       <c r="O83">
-        <v>-0.4493952734133003</v>
+        <v>-0.4581373385171683</v>
       </c>
       <c r="P83">
-        <v>-2.628654544486017</v>
+        <v>-2.67978963762782</v>
       </c>
       <c r="Q83">
-        <v>-1.985654544486017</v>
+        <v>-2.03678963762782</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3410697032678881</v>
+        <v>0.3574735756716597</v>
       </c>
       <c r="T83">
-        <v>6.819161738288411</v>
+        <v>7.198004057082212</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05334213249629153</v>
+        <v>0.05269161868536113</v>
       </c>
       <c r="W83">
-        <v>0.2232219251573745</v>
+        <v>0.2233753163139919</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3653570718924076</v>
+        <v>0.3609014978449393</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2475130029983721</v>
+        <v>0.249413002998372</v>
       </c>
       <c r="C84">
-        <v>-10.5994876279696</v>
+        <v>-10.9220419700663</v>
       </c>
       <c r="D84">
-        <v>8.032933814545192</v>
+        <v>7.964311441259641</v>
       </c>
       <c r="E84">
-        <v>16.9292245613992</v>
+        <v>17.18315653021035</v>
       </c>
       <c r="F84">
-        <v>20.82242144251479</v>
+        <v>21.07635341132594</v>
       </c>
       <c r="G84">
         <v>2.19</v>
@@ -8163,37 +8163,37 @@
         <v>1.772</v>
       </c>
       <c r="M84">
-        <v>4.909926976144988</v>
+        <v>4.969804134390658</v>
       </c>
       <c r="N84">
-        <v>-3.137926976144988</v>
+        <v>-3.197804134390658</v>
       </c>
       <c r="O84">
-        <v>-0.4581373385171683</v>
+        <v>-0.4668794036210361</v>
       </c>
       <c r="P84">
-        <v>-2.67978963762782</v>
+        <v>-2.730924730769622</v>
       </c>
       <c r="Q84">
-        <v>-2.03678963762782</v>
+        <v>-2.087924730769622</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3574735756716597</v>
+        <v>0.3758073154170514</v>
       </c>
       <c r="T84">
-        <v>7.198004057082212</v>
+        <v>7.62141606043999</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05269161868536113</v>
+        <v>0.05205677990601944</v>
       </c>
       <c r="W84">
-        <v>0.2233753163139919</v>
+        <v>0.2235250112981606</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3609014978449393</v>
+        <v>0.3565532870275304</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.249413002998372</v>
+        <v>0.2513130029983721</v>
       </c>
       <c r="C85">
-        <v>-10.9220419700663</v>
+        <v>-11.24343381201954</v>
       </c>
       <c r="D85">
-        <v>7.964311441259641</v>
+        <v>7.896851568117557</v>
       </c>
       <c r="E85">
-        <v>17.18315653021035</v>
+        <v>17.43708849902151</v>
       </c>
       <c r="F85">
-        <v>21.07635341132594</v>
+        <v>21.3302853801371</v>
       </c>
       <c r="G85">
         <v>2.19</v>
@@ -8245,37 +8245,37 @@
         <v>1.772</v>
       </c>
       <c r="M85">
-        <v>4.969804134390658</v>
+        <v>5.029681292636328</v>
       </c>
       <c r="N85">
-        <v>-3.197804134390658</v>
+        <v>-3.257681292636328</v>
       </c>
       <c r="O85">
-        <v>-0.4668794036210361</v>
+        <v>-0.4756214687249039</v>
       </c>
       <c r="P85">
-        <v>-2.730924730769622</v>
+        <v>-2.782059823911424</v>
       </c>
       <c r="Q85">
-        <v>-2.087924730769622</v>
+        <v>-2.139059823911424</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3758073154170514</v>
+        <v>0.3964327726306172</v>
       </c>
       <c r="T85">
-        <v>7.62141606043999</v>
+        <v>8.097754564217491</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05205677990601944</v>
+        <v>0.05143705633570969</v>
       </c>
       <c r="W85">
-        <v>0.2235250112981606</v>
+        <v>0.2236711421160397</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3565532870275304</v>
+        <v>0.3523086050391074</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2513130029983721</v>
+        <v>0.253213002998372</v>
       </c>
       <c r="C86">
-        <v>-11.24343381201954</v>
+        <v>-11.56369244579087</v>
       </c>
       <c r="D86">
-        <v>7.896851568117557</v>
+        <v>7.830524903157384</v>
       </c>
       <c r="E86">
-        <v>17.43708849902151</v>
+        <v>17.69102046783266</v>
       </c>
       <c r="F86">
-        <v>21.3302853801371</v>
+        <v>21.58421734894825</v>
       </c>
       <c r="G86">
         <v>2.19</v>
@@ -8327,37 +8327,37 @@
         <v>1.772</v>
       </c>
       <c r="M86">
-        <v>5.029681292636328</v>
+        <v>5.089558450881999</v>
       </c>
       <c r="N86">
-        <v>-3.257681292636328</v>
+        <v>-3.317558450881999</v>
       </c>
       <c r="O86">
-        <v>-0.4756214687249039</v>
+        <v>-0.4843635338287718</v>
       </c>
       <c r="P86">
-        <v>-2.782059823911424</v>
+        <v>-2.833194917053227</v>
       </c>
       <c r="Q86">
-        <v>-2.139059823911424</v>
+        <v>-2.190194917053227</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.396432772630617</v>
+        <v>0.4198082908059915</v>
       </c>
       <c r="T86">
-        <v>8.097754564217485</v>
+        <v>8.637604868498652</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05143705633570969</v>
+        <v>0.05083191449646605</v>
       </c>
       <c r="W86">
-        <v>0.2236711421160397</v>
+        <v>0.2238138345617333</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3523086050391074</v>
+        <v>0.3481637979210003</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.253213002998372</v>
+        <v>0.255113002998372</v>
       </c>
       <c r="C87">
-        <v>-11.56369244579087</v>
+        <v>-11.88284618743095</v>
       </c>
       <c r="D87">
-        <v>7.830524903157384</v>
+        <v>7.76530313032846</v>
       </c>
       <c r="E87">
-        <v>17.69102046783266</v>
+        <v>17.94495243664382</v>
       </c>
       <c r="F87">
-        <v>21.58421734894825</v>
+        <v>21.83814931775941</v>
       </c>
       <c r="G87">
         <v>2.19</v>
@@ -8409,37 +8409,37 @@
         <v>1.772</v>
       </c>
       <c r="M87">
-        <v>5.089558450881999</v>
+        <v>5.149435609127669</v>
       </c>
       <c r="N87">
-        <v>-3.317558450881999</v>
+        <v>-3.377435609127669</v>
       </c>
       <c r="O87">
-        <v>-0.4843635338287718</v>
+        <v>-0.4931055989326397</v>
       </c>
       <c r="P87">
-        <v>-2.833194917053227</v>
+        <v>-2.88433001019503</v>
       </c>
       <c r="Q87">
-        <v>-2.190194917053227</v>
+        <v>-2.241330010195029</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4198082908059915</v>
+        <v>0.4465231687207052</v>
       </c>
       <c r="T87">
-        <v>8.637604868498652</v>
+        <v>9.254576644819984</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05083191449646605</v>
+        <v>0.05024084572325133</v>
       </c>
       <c r="W87">
-        <v>0.2238138345617333</v>
+        <v>0.2239532085784574</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3481637979210003</v>
+        <v>0.344115381666105</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.255113002998372</v>
+        <v>0.257013002998372</v>
       </c>
       <c r="C88">
-        <v>-11.88284618743095</v>
+        <v>-12.20092241738644</v>
       </c>
       <c r="D88">
-        <v>7.76530313032846</v>
+        <v>7.701158869184122</v>
       </c>
       <c r="E88">
-        <v>17.94495243664382</v>
+        <v>18.19888440545497</v>
       </c>
       <c r="F88">
-        <v>21.83814931775941</v>
+        <v>22.09208128657056</v>
       </c>
       <c r="G88">
         <v>2.19</v>
@@ -8491,37 +8491,37 @@
         <v>1.772</v>
       </c>
       <c r="M88">
-        <v>5.149435609127669</v>
+        <v>5.20931276737334</v>
       </c>
       <c r="N88">
-        <v>-3.377435609127669</v>
+        <v>-3.43731276737334</v>
       </c>
       <c r="O88">
-        <v>-0.4931055989326397</v>
+        <v>-0.5018476640365077</v>
       </c>
       <c r="P88">
-        <v>-2.88433001019503</v>
+        <v>-2.935465103336833</v>
       </c>
       <c r="Q88">
-        <v>-2.241330010195029</v>
+        <v>-2.292465103336832</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4465231687207052</v>
+        <v>0.4773480278530671</v>
       </c>
       <c r="T88">
-        <v>9.254576644819984</v>
+        <v>9.966467155959982</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05024084572325133</v>
+        <v>0.04966336473792659</v>
       </c>
       <c r="W88">
-        <v>0.2239532085784574</v>
+        <v>0.2240893785947969</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.344115381666105</v>
+        <v>0.340160032451552</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.257013002998372</v>
+        <v>0.2589130029983721</v>
       </c>
       <c r="C89">
-        <v>-12.20092241738644</v>
+        <v>-12.51794761882562</v>
       </c>
       <c r="D89">
-        <v>7.701158869184122</v>
+        <v>7.638065636556105</v>
       </c>
       <c r="E89">
-        <v>18.19888440545497</v>
+        <v>18.45281637426613</v>
       </c>
       <c r="F89">
-        <v>22.09208128657056</v>
+        <v>22.34601325538172</v>
       </c>
       <c r="G89">
         <v>2.19</v>
@@ -8573,37 +8573,37 @@
         <v>1.772</v>
       </c>
       <c r="M89">
-        <v>5.20931276737334</v>
+        <v>5.26918992561901</v>
       </c>
       <c r="N89">
-        <v>-3.43731276737334</v>
+        <v>-3.49718992561901</v>
       </c>
       <c r="O89">
-        <v>-0.5018476640365077</v>
+        <v>-0.5105897291403755</v>
       </c>
       <c r="P89">
-        <v>-2.935465103336833</v>
+        <v>-2.986600196478635</v>
       </c>
       <c r="Q89">
-        <v>-2.292465103336832</v>
+        <v>-2.343600196478635</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4773480278530671</v>
+        <v>0.5133103635074894</v>
       </c>
       <c r="T89">
-        <v>9.966467155959982</v>
+        <v>10.79700608562332</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04966336473792659</v>
+        <v>0.04909900832045016</v>
       </c>
       <c r="W89">
-        <v>0.2240893785947969</v>
+        <v>0.2242224538380379</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.340160032451552</v>
+        <v>0.3362945775373298</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2589130029983721</v>
+        <v>0.260813002998372</v>
       </c>
       <c r="C90">
-        <v>-12.51794761882562</v>
+        <v>-12.83394741409527</v>
       </c>
       <c r="D90">
-        <v>7.638065636556105</v>
+        <v>7.575997810097613</v>
       </c>
       <c r="E90">
-        <v>18.45281637426613</v>
+        <v>18.70674834307729</v>
       </c>
       <c r="F90">
-        <v>22.34601325538172</v>
+        <v>22.59994522419288</v>
       </c>
       <c r="G90">
         <v>2.19</v>
@@ -8655,37 +8655,37 @@
         <v>1.772</v>
       </c>
       <c r="M90">
-        <v>5.26918992561901</v>
+        <v>5.329067083864681</v>
       </c>
       <c r="N90">
-        <v>-3.49718992561901</v>
+        <v>-3.557067083864681</v>
       </c>
       <c r="O90">
-        <v>-0.5105897291403755</v>
+        <v>-0.5193317942442435</v>
       </c>
       <c r="P90">
-        <v>-2.986600196478635</v>
+        <v>-3.037735289620438</v>
       </c>
       <c r="Q90">
-        <v>-2.343600196478635</v>
+        <v>-2.394735289620438</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5133103635074894</v>
+        <v>0.5558113056445338</v>
       </c>
       <c r="T90">
-        <v>10.79700608562332</v>
+        <v>11.77855209340725</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04909900832045016</v>
+        <v>0.04854733406965858</v>
       </c>
       <c r="W90">
-        <v>0.2242224538380379</v>
+        <v>0.2243525386263745</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3362945775373298</v>
+        <v>0.3325159867784834</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.260813002998372</v>
+        <v>0.2627130029983721</v>
       </c>
       <c r="C91">
-        <v>-12.83394741409527</v>
+        <v>-13.14894659941451</v>
       </c>
       <c r="D91">
-        <v>7.575997810097613</v>
+        <v>7.514930593589525</v>
       </c>
       <c r="E91">
-        <v>18.70674834307729</v>
+        <v>18.96068031188844</v>
       </c>
       <c r="F91">
-        <v>22.59994522419288</v>
+        <v>22.85387719300403</v>
       </c>
       <c r="G91">
         <v>2.19</v>
@@ -8737,37 +8737,37 @@
         <v>1.772</v>
       </c>
       <c r="M91">
-        <v>5.329067083864681</v>
+        <v>5.388944242110352</v>
       </c>
       <c r="N91">
-        <v>-3.557067083864681</v>
+        <v>-3.616944242110352</v>
       </c>
       <c r="O91">
-        <v>-0.5193317942442435</v>
+        <v>-0.5280738593481115</v>
       </c>
       <c r="P91">
-        <v>-3.037735289620438</v>
+        <v>-3.088870382762241</v>
       </c>
       <c r="Q91">
-        <v>-2.394735289620438</v>
+        <v>-2.445870382762241</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5558113056445338</v>
+        <v>0.6068124362089874</v>
       </c>
       <c r="T91">
-        <v>11.77855209340725</v>
+        <v>12.95640730274798</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04854733406965858</v>
+        <v>0.04800791924666237</v>
       </c>
       <c r="W91">
-        <v>0.2243525386263745</v>
+        <v>0.224479732641637</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3325159867784834</v>
+        <v>0.3288213647031669</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2627130029983721</v>
+        <v>0.264613002998372</v>
       </c>
       <c r="C92">
-        <v>-13.14894659941451</v>
+        <v>-13.46296917790402</v>
       </c>
       <c r="D92">
-        <v>7.514930593589525</v>
+        <v>7.454839983911172</v>
       </c>
       <c r="E92">
-        <v>18.96068031188844</v>
+        <v>19.2146122806996</v>
       </c>
       <c r="F92">
-        <v>22.85387719300403</v>
+        <v>23.10780916181519</v>
       </c>
       <c r="G92">
         <v>2.19</v>
@@ -8819,37 +8819,37 @@
         <v>1.772</v>
       </c>
       <c r="M92">
-        <v>5.388944242110352</v>
+        <v>5.448821400356022</v>
       </c>
       <c r="N92">
-        <v>-3.616944242110352</v>
+        <v>-3.676821400356022</v>
       </c>
       <c r="O92">
-        <v>-0.5280738593481115</v>
+        <v>-0.5368159244519792</v>
       </c>
       <c r="P92">
-        <v>-3.088870382762241</v>
+        <v>-3.140005475904043</v>
       </c>
       <c r="Q92">
-        <v>-2.445870382762241</v>
+        <v>-2.497005475904043</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6068124362089874</v>
+        <v>0.6691471513433193</v>
       </c>
       <c r="T92">
-        <v>12.95640730274798</v>
+        <v>14.39600811416442</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04800791924666237</v>
+        <v>0.04748035969450125</v>
       </c>
       <c r="W92">
-        <v>0.224479732641637</v>
+        <v>0.2246041311840366</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3288213647031669</v>
+        <v>0.3252079431130223</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.264613002998372</v>
+        <v>0.2665130029983721</v>
       </c>
       <c r="C93">
-        <v>-13.46296917790402</v>
+        <v>-13.77603839104322</v>
       </c>
       <c r="D93">
-        <v>7.454839983911172</v>
+        <v>7.395702739583125</v>
       </c>
       <c r="E93">
-        <v>19.2146122806996</v>
+        <v>19.46854424951075</v>
       </c>
       <c r="F93">
-        <v>23.10780916181519</v>
+        <v>23.36174113062635</v>
       </c>
       <c r="G93">
         <v>2.19</v>
@@ -8901,37 +8901,37 @@
         <v>1.772</v>
       </c>
       <c r="M93">
-        <v>5.448821400356022</v>
+        <v>5.508698558601693</v>
       </c>
       <c r="N93">
-        <v>-3.676821400356022</v>
+        <v>-3.736698558601693</v>
       </c>
       <c r="O93">
-        <v>-0.5368159244519792</v>
+        <v>-0.5455579895558472</v>
       </c>
       <c r="P93">
-        <v>-3.140005475904043</v>
+        <v>-3.191140569045846</v>
       </c>
       <c r="Q93">
-        <v>-2.497005475904043</v>
+        <v>-2.548140569045846</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6691471513433193</v>
+        <v>0.7470655452612346</v>
       </c>
       <c r="T93">
-        <v>14.39600811416442</v>
+        <v>16.19550912843498</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04748035969450125</v>
+        <v>0.04696426882825667</v>
       </c>
       <c r="W93">
-        <v>0.2246041311840366</v>
+        <v>0.2247258254102971</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3252079431130223</v>
+        <v>0.3216730741661415</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2665130029983721</v>
+        <v>0.2684130029983721</v>
       </c>
       <c r="C94">
-        <v>-13.77603839104322</v>
+        <v>-14.08817674864201</v>
       </c>
       <c r="D94">
-        <v>7.395702739583125</v>
+        <v>7.337496350795488</v>
       </c>
       <c r="E94">
-        <v>19.46854424951075</v>
+        <v>19.72247621832191</v>
       </c>
       <c r="F94">
-        <v>23.36174113062635</v>
+        <v>23.6156730994375</v>
       </c>
       <c r="G94">
         <v>2.19</v>
@@ -8983,37 +8983,37 @@
         <v>1.772</v>
       </c>
       <c r="M94">
-        <v>5.508698558601693</v>
+        <v>5.568575716847363</v>
       </c>
       <c r="N94">
-        <v>-3.736698558601693</v>
+        <v>-3.796575716847364</v>
       </c>
       <c r="O94">
-        <v>-0.5455579895558472</v>
+        <v>-0.554300054659715</v>
       </c>
       <c r="P94">
-        <v>-3.191140569045846</v>
+        <v>-3.242275662187649</v>
       </c>
       <c r="Q94">
-        <v>-2.548140569045846</v>
+        <v>-2.599275662187648</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7470655452612346</v>
+        <v>0.8472463374414108</v>
       </c>
       <c r="T94">
-        <v>16.19550912843498</v>
+        <v>18.50915328963998</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04696426882825667</v>
+        <v>0.04645927669031843</v>
       </c>
       <c r="W94">
-        <v>0.2247258254102971</v>
+        <v>0.2248449025564229</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3216730741661415</v>
+        <v>0.3182142239062906</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2684130029983721</v>
+        <v>0.270313002998372</v>
       </c>
       <c r="C95">
-        <v>-14.08817674864201</v>
+        <v>-14.39940605740822</v>
       </c>
       <c r="D95">
-        <v>7.337496350795488</v>
+        <v>7.280199010840444</v>
       </c>
       <c r="E95">
-        <v>19.72247621832191</v>
+        <v>19.97640818713307</v>
       </c>
       <c r="F95">
-        <v>23.6156730994375</v>
+        <v>23.86960506824866</v>
       </c>
       <c r="G95">
         <v>2.19</v>
@@ -9065,37 +9065,37 @@
         <v>1.772</v>
       </c>
       <c r="M95">
-        <v>5.568575716847363</v>
+        <v>5.628452875093034</v>
       </c>
       <c r="N95">
-        <v>-3.796575716847364</v>
+        <v>-3.856452875093034</v>
       </c>
       <c r="O95">
-        <v>-0.554300054659715</v>
+        <v>-0.563042119763583</v>
       </c>
       <c r="P95">
-        <v>-3.242275662187649</v>
+        <v>-3.293410755329452</v>
       </c>
       <c r="Q95">
-        <v>-2.599275662187648</v>
+        <v>-2.650410755329451</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8472463374414108</v>
+        <v>0.9808207270149796</v>
       </c>
       <c r="T95">
-        <v>18.50915328963998</v>
+        <v>21.59401217124665</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04645927669031843</v>
+        <v>0.04596502906595334</v>
       </c>
       <c r="W95">
-        <v>0.2248449025564229</v>
+        <v>0.2249614461462482</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3182142239062906</v>
+        <v>0.3148289662051598</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.270313002998372</v>
+        <v>0.272213002998372</v>
       </c>
       <c r="C96">
-        <v>-14.39940605740822</v>
+        <v>-14.70974744818692</v>
       </c>
       <c r="D96">
-        <v>7.280199010840444</v>
+        <v>7.223789588872897</v>
       </c>
       <c r="E96">
-        <v>19.97640818713307</v>
+        <v>20.23034015594422</v>
       </c>
       <c r="F96">
-        <v>23.86960506824866</v>
+        <v>24.12353703705982</v>
       </c>
       <c r="G96">
         <v>2.19</v>
@@ -9147,37 +9147,37 @@
         <v>1.772</v>
       </c>
       <c r="M96">
-        <v>5.628452875093034</v>
+        <v>5.688330033338705</v>
       </c>
       <c r="N96">
-        <v>-3.856452875093034</v>
+        <v>-3.916330033338705</v>
       </c>
       <c r="O96">
-        <v>-0.563042119763583</v>
+        <v>-0.571784184867451</v>
       </c>
       <c r="P96">
-        <v>-3.293410755329452</v>
+        <v>-3.344545848471254</v>
       </c>
       <c r="Q96">
-        <v>-2.650410755329451</v>
+        <v>-2.701545848471254</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9808207270149796</v>
+        <v>1.167824872417976</v>
       </c>
       <c r="T96">
-        <v>21.59401217124665</v>
+        <v>25.91281460549599</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04596502906595334</v>
+        <v>0.04548118665473277</v>
       </c>
       <c r="W96">
-        <v>0.2249614461462482</v>
+        <v>0.225075536186814</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3148289662051598</v>
+        <v>0.3115149770872108</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.272213002998372</v>
+        <v>0.2741130029983721</v>
       </c>
       <c r="C97">
-        <v>-14.70974744818692</v>
+        <v>-15.01922140194323</v>
       </c>
       <c r="D97">
-        <v>7.223789588872897</v>
+        <v>7.168247603927743</v>
       </c>
       <c r="E97">
-        <v>20.23034015594422</v>
+        <v>20.48427212475538</v>
       </c>
       <c r="F97">
-        <v>24.12353703705982</v>
+        <v>24.37746900587097</v>
       </c>
       <c r="G97">
         <v>2.19</v>
@@ -9229,37 +9229,37 @@
         <v>1.772</v>
       </c>
       <c r="M97">
-        <v>5.688330033338705</v>
+        <v>5.748207191584375</v>
       </c>
       <c r="N97">
-        <v>-3.916330033338705</v>
+        <v>-3.976207191584376</v>
       </c>
       <c r="O97">
-        <v>-0.571784184867451</v>
+        <v>-0.5805262499713187</v>
       </c>
       <c r="P97">
-        <v>-3.344545848471254</v>
+        <v>-3.395680941613057</v>
       </c>
       <c r="Q97">
-        <v>-2.701545848471254</v>
+        <v>-2.752680941613057</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.167824872417976</v>
+        <v>1.448331090522471</v>
       </c>
       <c r="T97">
-        <v>25.91281460549599</v>
+        <v>32.39101825687001</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04548118665473277</v>
+        <v>0.04500742429374598</v>
       </c>
       <c r="W97">
-        <v>0.225075536186814</v>
+        <v>0.2251872493515347</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3115149770872108</v>
+        <v>0.308270029409219</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.274113002998372</v>
+        <v>0.2760130029983721</v>
       </c>
       <c r="C98">
-        <v>-15.01922140194322</v>
+        <v>-15.32784777455548</v>
       </c>
       <c r="D98">
-        <v>7.168247603927743</v>
+        <v>7.113553200126645</v>
       </c>
       <c r="E98">
-        <v>20.48427212475537</v>
+        <v>20.73820409356653</v>
       </c>
       <c r="F98">
-        <v>24.37746900587097</v>
+        <v>24.63140097468212</v>
       </c>
       <c r="G98">
         <v>2.19</v>
@@ -9311,37 +9311,37 @@
         <v>1.772</v>
       </c>
       <c r="M98">
-        <v>5.748207191584374</v>
+        <v>5.808084349830045</v>
       </c>
       <c r="N98">
-        <v>-3.976207191584375</v>
+        <v>-4.036084349830046</v>
       </c>
       <c r="O98">
-        <v>-0.5805262499713186</v>
+        <v>-0.5892683150751866</v>
       </c>
       <c r="P98">
-        <v>-3.395680941613056</v>
+        <v>-3.446816034754859</v>
       </c>
       <c r="Q98">
-        <v>-2.752680941613056</v>
+        <v>-2.803816034754859</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.448331090522467</v>
+        <v>1.915841454029956</v>
       </c>
       <c r="T98">
-        <v>32.39101825686992</v>
+        <v>43.18802434249323</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04500742429374598</v>
+        <v>0.044543430228862</v>
       </c>
       <c r="W98">
-        <v>0.2251872493515347</v>
+        <v>0.2252966591520344</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.308270029409219</v>
+        <v>0.3050919878689178</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2760130029983721</v>
+        <v>0.2779130029983721</v>
       </c>
       <c r="C99">
-        <v>-15.32784777455548</v>
+        <v>-15.63564582048202</v>
       </c>
       <c r="D99">
-        <v>7.113553200126645</v>
+        <v>7.059687123011258</v>
       </c>
       <c r="E99">
-        <v>20.73820409356653</v>
+        <v>20.99213606237769</v>
       </c>
       <c r="F99">
-        <v>24.63140097468212</v>
+        <v>24.88533294349328</v>
       </c>
       <c r="G99">
         <v>2.19</v>
@@ -9393,37 +9393,37 @@
         <v>1.772</v>
       </c>
       <c r="M99">
-        <v>5.808084349830045</v>
+        <v>5.867961508075716</v>
       </c>
       <c r="N99">
-        <v>-4.036084349830046</v>
+        <v>-4.095961508075717</v>
       </c>
       <c r="O99">
-        <v>-0.5892683150751866</v>
+        <v>-0.5980103801790546</v>
       </c>
       <c r="P99">
-        <v>-3.446816034754859</v>
+        <v>-3.497951127896662</v>
       </c>
       <c r="Q99">
-        <v>-2.803816034754859</v>
+        <v>-2.854951127896662</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.915841454029956</v>
+        <v>2.850862181044934</v>
       </c>
       <c r="T99">
-        <v>43.18802434249323</v>
+        <v>64.78203651373984</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.044543430228862</v>
+        <v>0.0440889054306083</v>
       </c>
       <c r="W99">
-        <v>0.2252966591520344</v>
+        <v>0.2254038360994626</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3050919878689178</v>
+        <v>0.301978804319235</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2779130029983721</v>
+        <v>0.279813002998372</v>
       </c>
       <c r="C100">
-        <v>-15.63564582048202</v>
+        <v>-15.9426342153608</v>
       </c>
       <c r="D100">
-        <v>7.059687123011258</v>
+        <v>7.006630696943635</v>
       </c>
       <c r="E100">
-        <v>20.99213606237769</v>
+        <v>21.24606803118884</v>
       </c>
       <c r="F100">
-        <v>24.88533294349328</v>
+        <v>25.13926491230444</v>
       </c>
       <c r="G100">
         <v>2.19</v>
@@ -9475,37 +9475,37 @@
         <v>1.772</v>
       </c>
       <c r="M100">
-        <v>5.867961508075716</v>
+        <v>5.927838666321387</v>
       </c>
       <c r="N100">
-        <v>-4.095961508075717</v>
+        <v>-4.155838666321388</v>
       </c>
       <c r="O100">
-        <v>-0.5980103801790546</v>
+        <v>-0.6067524452829225</v>
       </c>
       <c r="P100">
-        <v>-3.497951127896662</v>
+        <v>-3.549086221038465</v>
       </c>
       <c r="Q100">
-        <v>-2.854951127896662</v>
+        <v>-2.906086221038465</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.850862181044934</v>
+        <v>5.655924362089868</v>
       </c>
       <c r="T100">
-        <v>64.78203651373984</v>
+        <v>129.5640730274797</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0440889054306083</v>
+        <v>0.04364356295151125</v>
       </c>
       <c r="W100">
-        <v>0.2254038360994626</v>
+        <v>0.2255088478560336</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.301978804319235</v>
+        <v>0.2989285133665154</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.279813002998372</v>
-      </c>
-      <c r="C101">
-        <v>-15.9426342153608</v>
-      </c>
-      <c r="D101">
-        <v>7.006630696943635</v>
-      </c>
-      <c r="E101">
-        <v>21.24606803118884</v>
-      </c>
-      <c r="F101">
-        <v>25.13926491230444</v>
-      </c>
-      <c r="G101">
-        <v>2.19</v>
-      </c>
-      <c r="H101">
-        <v>21.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.415</v>
-      </c>
-      <c r="K101">
-        <v>0.643</v>
-      </c>
-      <c r="L101">
-        <v>1.772</v>
-      </c>
-      <c r="M101">
-        <v>5.927838666321387</v>
-      </c>
-      <c r="N101">
-        <v>-4.155838666321388</v>
-      </c>
-      <c r="O101">
-        <v>-0.6067524452829225</v>
-      </c>
-      <c r="P101">
-        <v>-3.549086221038465</v>
-      </c>
-      <c r="Q101">
-        <v>-2.906086221038465</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.655924362089868</v>
-      </c>
-      <c r="T101">
-        <v>129.5640730274797</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04364356295151125</v>
-      </c>
-      <c r="W101">
-        <v>0.2255088478560336</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2989285133665154</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
